--- a/杭州9区初中梯队总表_整理版.xlsx
+++ b/杭州9区初中梯队总表_整理版.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I311"/>
+  <dimension ref="A1:I310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2133,22 +2133,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>上城区</t>
+          <t>拱墅区</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>采荷濮家</t>
+          <t>上海世外附属学校</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>采荷教育集团</t>
+          <t>拱墅区国际化民办</t>
         </is>
       </c>
     </row>
@@ -2176,20 +2176,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>上海世外附属学校</t>
+          <t>华东师范大学附属杭州学校</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>公办九年一贯制（内设初中部）</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>拱墅区国际化民办</t>
+          <t>华师大合作办学，拱墅区热门公办一梯队</t>
         </is>
       </c>
     </row>
@@ -2204,37 +2216,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>华东师范大学附属杭州学校</t>
+          <t>杭州上海世界外国语中学</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>无数据</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>华师大合作办学，拱墅区热门公办一梯队</t>
+          <t>双语国际化特色，以国际路线为主</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2261,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>杭州上海世界外国语中学</t>
+          <t>杭州启正中学</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2269,17 +2281,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>双语国际化特色，以国际路线为主</t>
+          <t>拱墅区老牌优质民办初中，一梯队民办</t>
         </is>
       </c>
     </row>
@@ -2294,17 +2306,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>杭州启正中学</t>
+          <t>杭州市北苑实验中学</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2314,17 +2326,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>拱墅区老牌优质民办初中，一梯队民办</t>
+          <t>拱墅北部公办初中，三梯队公办</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2356,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>杭州市北苑实验中学</t>
+          <t>杭州市启航中学</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2359,17 +2371,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>无数据</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>拱墅北部公办初中，三梯队公办</t>
+          <t>北部板块公办</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2396,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>杭州市启航中学</t>
+          <t>杭州市和睦中学</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2402,21 +2414,9 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>无数据</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>北部板块公办</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>杭州市和睦中学</t>
+          <t>杭州市大关中学教育集团</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2447,9 +2447,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>大关中学教育集团总校，拱墅区老牌公办</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2467,7 +2479,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>杭州市大关中学教育集团</t>
+          <t>杭州市大关实验中学</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2477,22 +2489,22 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>大关中学教育集团总校，拱墅区老牌公办</t>
+          <t>大关中学教育集团实验校区，二梯队公办，2026年分配生76人</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2519,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>杭州市大关实验中学</t>
+          <t>杭州市大成实验学校</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2522,24 +2534,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>大关中学教育集团实验校区，二梯队公办，2026年分配生76人</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>杭州市大成实验学校</t>
+          <t>杭州市大成岳家湾实验学校</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2567,12 +2567,24 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>公办独立初中</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>拱墅区老牌公办初中，三梯队公办</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2585,12 +2597,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>杭州市大成岳家湾实验学校</t>
+          <t>杭州市安吉路实验学校</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2600,22 +2612,22 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>拱墅区老牌公办初中，三梯队公办</t>
+          <t>拱墅区老牌九年一贯制名校，一梯队公办</t>
         </is>
       </c>
     </row>
@@ -2630,12 +2642,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>杭州市安吉路实验学校</t>
+          <t>杭州市小河中学</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2645,24 +2657,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>拱墅区老牌九年一贯制名校，一梯队公办</t>
-        </is>
-      </c>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>杭州市小河中学</t>
+          <t>杭州市康桥中学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2693,9 +2693,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>康桥板块老牌公办初中，三梯队公办</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2713,7 +2725,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>杭州市康桥中学</t>
+          <t>杭州市慧澜中学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2723,22 +2735,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>康桥板块老牌公办初中，三梯队公办</t>
+          <t>拱墅区北部公办初中，三梯队公办</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2770,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>杭州市慧澜中学</t>
+          <t>杭州市拱宸中学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2768,22 +2780,22 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>拱墅区北部公办初中，三梯队公办</t>
+          <t>拱宸桥街道老牌公办初中，规模较大，三梯队公办</t>
         </is>
       </c>
     </row>
@@ -2798,12 +2810,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>杭州市拱宸中学</t>
+          <t>杭州市拱宸桥中学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2816,21 +2828,9 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>拱宸桥街道老牌公办初中，规模较大，三梯队公办</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>杭州市拱宸桥中学</t>
+          <t>杭州市文晖中学</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2861,9 +2861,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>文晖板块老牌公办</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2881,7 +2893,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>杭州市文晖中学</t>
+          <t>杭州市文晖实验学校</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2896,17 +2908,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>文晖板块老牌公办</t>
+          <t>拱墅区热门公办初中，二梯队公办</t>
         </is>
       </c>
     </row>
@@ -2921,17 +2933,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>杭州市文晖实验学校</t>
+          <t>杭州市文澜中学</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>公办（民转公）</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2941,17 +2953,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>拱墅区热门公办初中，二梯队公办</t>
+          <t>2026年停止招生</t>
         </is>
       </c>
     </row>
@@ -2971,12 +2983,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>杭州市文澜中学</t>
+          <t>杭州市文澜实验中学（慧澜校区）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>公办（民转公）</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2986,17 +2998,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026年停止招生</t>
+          <t>文澜教育集团核心公办初中，拱墅区公办一梯队，2026年分配生94人</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3023,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>杭州市文澜实验中学（慧澜校区）</t>
+          <t>杭州市文澜实验学校</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3026,22 +3038,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>文澜教育集团核心公办初中，拱墅区公办一梯队，2026年分配生94人</t>
+          <t>文澜系公办</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3060,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>杭州市文澜实验学校</t>
+          <t>杭州市明德中学</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3071,16 +3075,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>文澜系公办</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>杭州市明德中学</t>
+          <t>杭州市明珠实验学校</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3108,12 +3108,24 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>拱墅区大型公办九年一贯制学校，三梯队公办</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3126,39 +3138,23 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>杭州市明珠实验学校</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>公办</t>
-        </is>
-      </c>
+          <t>杭州市星澜中学</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>拱墅区大型公办九年一贯制学校，三梯队公办</t>
-        </is>
-      </c>
+          <t>公办初中</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3171,23 +3167,39 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>杭州市星澜中学</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>杭州市春蕾中学</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>公办</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>公办初中</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>含王马、仙林两个校区</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3200,12 +3212,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>杭州市春蕾中学</t>
+          <t>杭州市景成实验学校</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3215,22 +3227,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>含王马、仙林两个校区</t>
+          <t>北景园板块公办初中，三梯队公办</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3257,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>杭州市景成实验学校</t>
+          <t>杭州市朝晖中学</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3260,22 +3272,22 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>北景园板块公办初中，三梯队公办</t>
+          <t>朝晖板块老牌公办初中，二梯队公办</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3302,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>杭州市朝晖中学</t>
+          <t>杭州市桃源中学</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3310,17 +3322,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>朝晖板块老牌公办初中，二梯队公办</t>
+          <t>半山桃源板块公办初中，三梯队公办</t>
         </is>
       </c>
     </row>
@@ -3335,12 +3347,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>杭州市桃源中学</t>
+          <t>杭州市求是中学</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3350,24 +3362,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>半山桃源板块公办初中，三梯队公办</t>
-        </is>
-      </c>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>杭州市求是中学</t>
+          <t>杭州市源清中学</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>杭州市源清中学</t>
+          <t>杭州市育才东坡中学</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3431,9 +3431,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2024年成立</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3451,7 +3463,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>杭州市育才东坡中学</t>
+          <t>杭州市育才大城北学校</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3461,7 +3473,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3476,7 +3488,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2024年成立</t>
+          <t>育才集团托管九年一贯制</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3508,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>杭州市育才大城北学校</t>
+          <t>杭州市育才科技中学</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3506,7 +3518,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3521,7 +3533,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>育才集团托管九年一贯制</t>
+          <t>2025年正式启用</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3548,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>杭州市育才科技中学</t>
+          <t>杭州市胜蓝中学</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3554,21 +3566,9 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>无数据</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2025年正式启用</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>杭州市胜蓝中学</t>
+          <t>杭州市胜蓝实验学校</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3596,12 +3596,24 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+          <t>公办九年一贯制（内设初中部）</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>东新板块公办初中，三梯队公办</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3619,7 +3631,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>杭州市胜蓝实验学校</t>
+          <t>杭州市艮山中学</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3629,22 +3641,22 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>无数据</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>东新板块公办初中，三梯队公办</t>
+          <t>原下城区公办</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3671,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>杭州市艮山中学</t>
+          <t>杭州市行知中学</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3679,17 +3691,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>原下城区公办</t>
+          <t>拱墅区老牌公办初中，二梯队公办</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3716,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>杭州市行知中学</t>
+          <t>杭州市观成武林中学</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3724,17 +3736,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>拱墅区老牌公办初中，二梯队公办</t>
+          <t>观成教育集团核心公办，一梯队公办，2026年分配生96人</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3766,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>杭州市观成武林中学</t>
+          <t>杭州市锦绣中学</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3769,17 +3781,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>观成教育集团核心公办，一梯队公办，2026年分配生96人</t>
+          <t>锦绣育才教育集团核心民办，一梯队民办，2026年分配生114人</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3806,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>杭州市锦绣中学</t>
+          <t>杭州市锦绣育才中学附属学校</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3809,24 +3821,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>锦绣育才教育集团核心民办，一梯队民办，2026年分配生114人</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>杭州市锦绣育才中学附属学校</t>
+          <t>杭州市长征中学</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>杭州市长征中学</t>
+          <t>杭州市长阳中学</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3890,9 +3890,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>北部板块公办</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3910,7 +3922,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>杭州市长阳中学</t>
+          <t>杭州市青春中学</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3935,7 +3947,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>北部板块公办</t>
+          <t>原下城区老牌公办</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3962,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>杭州市青春中学</t>
+          <t>杭州市风华中学</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3965,22 +3977,22 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>原下城区老牌公办</t>
+          <t>半山板块公办初中，三梯队公办</t>
         </is>
       </c>
     </row>
@@ -3995,12 +4007,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>杭州市风华中学</t>
+          <t>杭州市风帆中学</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4010,22 +4022,22 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>半山板块公办初中，三梯队公办</t>
+          <t>朝晖板块老牌公办初中，二梯队公办</t>
         </is>
       </c>
     </row>
@@ -4040,17 +4052,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>杭州市风帆中学</t>
+          <t>杭州树兰中学</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4060,17 +4072,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>无数据</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>朝晖板块老牌公办初中，二梯队公办</t>
+          <t>半山板块民办，设国内班与特色班</t>
         </is>
       </c>
     </row>
@@ -4085,37 +4097,37 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>杭州树兰中学</t>
+          <t>杭州第十四中学附属学校</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>半山板块民办，设国内班与特色班</t>
+          <t>十四中教育集团附属学校，二梯队公办</t>
         </is>
       </c>
     </row>
@@ -4130,37 +4142,37 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>杭州第十四中学附属学校</t>
+          <t>杭州育才中学</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>十四中教育集团附属学校，二梯队公办</t>
+          <t>锦绣育才教育集团核心民办，拱墅区民办一梯队天花板，2026年分配生89人</t>
         </is>
       </c>
     </row>
@@ -4180,32 +4192,32 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>杭州育才中学</t>
+          <t>杭州观成实验学校（初中部）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办（民转公）</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>锦绣育才教育集团核心民办，拱墅区民办一梯队天花板，2026年分配生89人</t>
+          <t>2026年停止招生</t>
         </is>
       </c>
     </row>
@@ -4220,39 +4232,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>杭州观成实验学校（初中部）</t>
+          <t>浙江省杭州第十一中学</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>公办（民转公）</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2026年停止招生</t>
-        </is>
-      </c>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>拱墅区</t>
+          <t>西湖区</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>浙江省杭州第十一中学</t>
+          <t>三墩中学振华校区</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4283,8 +4283,16 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -4298,12 +4306,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>三墩中学振华校区</t>
+          <t>三墩中学文理校区</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4316,16 +4324,8 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>三墩中学文理校区</t>
+          <t>丰潭中学丰潭校区</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4357,9 +4357,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>暂无公开精确数据</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>西湖区公办普通校</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4372,12 +4384,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>丰潭中学丰潭校区</t>
+          <t>丰潭中学景汇校区</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4390,21 +4402,9 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>暂无公开精确数据</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>西湖区公办普通校</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>丰潭中学景汇校区</t>
+          <t>十三中教育集团（总校）嘉绿苑中学</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4435,9 +4435,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>443.90243902439</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>十三中教育集团</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4450,12 +4462,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>十三中教育集团（总校）嘉绿苑中学</t>
+          <t>十三中教育集团（总校）杭十三中</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4470,17 +4482,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>443.90243902439</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>224</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>十三中教育集团</t>
+          <t>西湖区公办老牌名校</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4507,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>十三中教育集团（总校）杭十三中</t>
+          <t>十五中教育集团（总校）崇德校区</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4515,19 +4527,15 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>西湖区公办老牌名校</t>
-        </is>
-      </c>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4540,12 +4548,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>十五中教育集团（总校）崇德校区</t>
+          <t>十五中教育集团（总校）浙大附初校区</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4558,16 +4566,8 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
@@ -4581,26 +4581,34 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>十五中教育集团（总校）浙大附初校区</t>
+          <t>杭州云谷学校（初中部）</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>暂无公开精确数据</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
@@ -4614,35 +4622,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>杭州云谷学校（初中部）</t>
+          <t>杭州外国语学校</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>暂无公开精确数据</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>全省招生，大量保送，不参与中考排名</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>杭州外国语学校</t>
+          <t>杭州市上泗中学</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4668,14 +4668,22 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>全省招生，大量保送，不参与中考排名</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>609.756097560976</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4688,35 +4696,39 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>杭州市上泗中学</t>
+          <t>杭州市东方中学</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>完全中学</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>609.756097560976</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>含初中、高中</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4729,37 +4741,37 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>杭州市东方中学</t>
+          <t>杭州市之江实验中学</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办（民转公）</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>完全中学</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253.658536585366</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>含初中、高中</t>
+          <t>2026年停止招生</t>
         </is>
       </c>
     </row>
@@ -4774,17 +4786,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>杭州市之江实验中学</t>
+          <t>杭州市仁和实验学校（初中部）</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>公办（民转公）</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4792,19 +4804,11 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>253.658536585366</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026年停止招生</t>
+          <t>西湖风景名胜区民办</t>
         </is>
       </c>
     </row>
@@ -4819,29 +4823,37 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>杭州市仁和实验学校（初中部）</t>
+          <t>杭州市保俶塔实验学校（初中部）</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>419.512195121951</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>西湖风景名胜区民办</t>
+          <t>保俶塔系本部</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4873,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>杭州市保俶塔实验学校（初中部）</t>
+          <t>杭州市保俶塔申花实验学校（初中部）</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4876,17 +4888,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>419.512195121951</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>保俶塔系本部</t>
+          <t>西湖区公办第一</t>
         </is>
       </c>
     </row>
@@ -4906,17 +4918,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>杭州市保俶塔申花实验学校（初中部）</t>
+          <t>杭州市公益中学</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>公办（民转公）</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4926,12 +4938,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>西湖区公办第一</t>
+          <t>2026年正常招生，需摇号</t>
         </is>
       </c>
     </row>
@@ -4946,39 +4958,35 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>杭州市公益中学</t>
+          <t>杭州市吉鸿中学</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>公办（民转公）</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2026年正常招生，需摇号</t>
-        </is>
-      </c>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4996,7 +5004,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>杭州市吉鸿中学</t>
+          <t>杭州市周浦中学</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5006,20 +5014,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>西湖区乡镇初中</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5032,12 +5044,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>杭州市周浦中学</t>
+          <t>杭州市弘益中学</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5052,19 +5064,15 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>448.780487804878</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>西湖区乡镇初中</t>
-        </is>
-      </c>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5082,7 +5090,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>杭州市弘益中学</t>
+          <t>杭州市文溪中学</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5097,12 +5105,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>448.780487804878</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -5123,7 +5131,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>杭州市文溪中学</t>
+          <t>杭州市文理中学</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5133,17 +5141,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -5159,12 +5167,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>杭州市文理中学</t>
+          <t>杭州市第十五中学教育集团・浙大附初校区</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5179,12 +5187,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>暂无公开精确数据</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -5200,12 +5208,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州市第十五中学教育集团・浙大附初校区</t>
+          <t>杭州市紫金港中学</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5215,20 +5223,24 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>暂无公开精确数据</t>
+          <t>424.390243902439</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>西湖区公办黑马，今年大爆发</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5241,12 +5253,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>杭州市紫金港中学</t>
+          <t>杭州市袁浦中学</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5261,17 +5273,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>424.390243902439</t>
+          <t>619.512195121951</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>西湖区公办黑马，今年大爆发</t>
+          <t>西湖区乡镇初中</t>
         </is>
       </c>
     </row>
@@ -5291,34 +5303,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>杭州市袁浦中学</t>
+          <t>杭州市西子实验学校（初中部）</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>十二年一贯制</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>619.512195121951</t>
+          <t>暂无公开精确数据</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>西湖区乡镇初中</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5336,17 +5344,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>杭州市西子实验学校（初中部）</t>
+          <t>杭州市西湖第一实验学校（初中部）</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5356,7 +5364,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -5372,12 +5380,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>杭州市西湖第一实验学校（初中部）</t>
+          <t>杭州市西溪中学</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5387,20 +5395,24 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>暂无公开精确数据</t>
+          <t>517.073170731707</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>西湖区公办第二梯队</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5413,12 +5425,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>杭州市西溪中学</t>
+          <t>杭州市西溪实验学校</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5428,24 +5440,20 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>517.073170731707</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>西湖区公办第二梯队</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5458,35 +5466,39 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>杭州市西溪实验学校</t>
+          <t>杭州绿城育华学校（初中部）</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>杭州老牌民办</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5499,39 +5511,35 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>杭州绿城育华学校（初中部）</t>
+          <t>浙江工业大学附属实验学校（初中部）</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>292.682926829268</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>杭州老牌民办</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5544,12 +5552,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>浙江工业大学附属实验学校（初中部）</t>
+          <t>翠苑中学文华校区</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5559,19 +5567,11 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>292.682926829268</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>翠苑中学文华校区</t>
+          <t>翠苑中学翠苑校区</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5603,9 +5603,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>356.09756097561</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>翠苑教育集团</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5613,42 +5625,30 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>西湖区</t>
+          <t>滨江区</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>翠苑中学翠苑校区</t>
+          <t>启正中学</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>356.09756097561</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>翠苑教育集团</t>
+          <t>小班化教学，前三率公办民办中领先</t>
         </is>
       </c>
     </row>
@@ -5663,12 +5663,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>启正中学</t>
+          <t>杭州上海世界外国语学校</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5676,14 +5676,14 @@
           <t>民办</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>十二年一贯制</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>小班化教学，前三率公办民办中领先</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5696,27 +5696,27 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>杭州上海世界外国语学校</t>
+          <t>杭州二中滨江校区初中部</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>杭二嫡系初中</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5734,20 +5734,32 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>杭州二中滨江校区初中部</t>
+          <t>杭州二中白马湖学校（初中部）</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+          <t>公办（民转公）</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>杭二嫡系初中</t>
+          <t>2026年正常招生，需摇号</t>
         </is>
       </c>
     </row>
@@ -5762,17 +5774,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>杭州二中白马湖学校（初中部）</t>
+          <t>杭州二中附属第一学校</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>公办（民转公）</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5782,19 +5794,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2026年正常招生，需摇号</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5807,34 +5815,26 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>杭州二中附属第一学校</t>
+          <t>杭州国际学校</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>十二年一贯制</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
@@ -5853,17 +5853,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>杭州国际学校</t>
+          <t>杭州奥体实验学校</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -5886,22 +5886,26 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>杭州奥体实验学校</t>
+          <t>杭州学军中学教育集团文渊中学</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>完全中学</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>含初中、高中</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5914,29 +5918,37 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州学军中学教育集团文渊中学</t>
+          <t>杭州市浦沿中学</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>完全中学</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>含初中、高中</t>
+          <t>滨江公办普通校</t>
         </is>
       </c>
     </row>
@@ -5951,12 +5963,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>杭州市浦沿中学</t>
+          <t>杭州市滨和中学</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5971,17 +5983,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>滨江公办普通校</t>
+          <t>（滨和教育集团）</t>
         </is>
       </c>
     </row>
@@ -5996,12 +6008,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>杭州市滨和中学</t>
+          <t>杭州市滨文中学</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6016,7 +6028,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6024,11 +6036,7 @@
           <t>68</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>（滨和教育集团）</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6041,12 +6049,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>杭州市滨文中学</t>
+          <t>杭州市硅谷中学</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6061,12 +6069,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -6082,12 +6090,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>杭州市硅谷中学</t>
+          <t>杭州市竺可桢学校</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6102,12 +6110,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -6123,12 +6131,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>杭州市竺可桢学校</t>
+          <t>杭州市西兴中学</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6143,15 +6151,19 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>（滨和教育集团）</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6164,12 +6176,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州市西兴中学</t>
+          <t>杭州市钱塘湾初级中学</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6182,21 +6194,9 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>（滨和教育集团）</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>杭州市钱塘湾初级中学</t>
+          <t>杭州市长河中学</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -6227,9 +6227,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>滨江公办普通校</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6242,12 +6254,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>杭州市长河中学</t>
+          <t>杭州市闻涛中学</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -6262,17 +6274,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>514</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>105</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>滨江公办普通校</t>
+          <t>滨江公办第二梯队</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6304,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>杭州市闻涛中学</t>
+          <t>杭州江南实验学校</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6302,22 +6314,22 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>滨江公办第二梯队</t>
+          <t>滨江公办老牌强校</t>
         </is>
       </c>
     </row>
@@ -6332,12 +6344,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>杭州江南实验学校</t>
+          <t>杭州湖畔学校</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6352,19 +6364,15 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>滨江公办老牌强校</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6377,35 +6385,39 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>杭州湖畔学校</t>
+          <t>杭州滨兰实验学校（初中部）</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>滨江区第二，优高率91%全市前列</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6418,17 +6430,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>杭州滨兰实验学校（初中部）</t>
+          <t>杭州高级中学附属滨江中学</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6438,19 +6450,15 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>滨江区第二，优高率91%全市前列</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6463,12 +6471,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>杭州高级中学附属滨江中学</t>
+          <t>浙江省杭州滨兴学校</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6478,17 +6486,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -6504,12 +6512,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>浙江省杭州滨兴学校</t>
+          <t>浙江省杭州高新实验学校</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -6524,15 +6532,19 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>730</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>滨江区公办第一</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6540,17 +6552,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>滨江区</t>
+          <t>钱塘区</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>浙江省杭州高新实验学校</t>
+          <t>临江一中</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6558,24 +6570,12 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>滨江区公办第一</t>
+          <t>钱塘区东部乡镇初中</t>
         </is>
       </c>
     </row>
@@ -6590,17 +6590,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>临江一中</t>
+          <t>养正中学</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>钱塘区东部乡镇初中</t>
+          <t>钱塘区民办第一，优高率近80%</t>
         </is>
       </c>
     </row>
@@ -6623,17 +6623,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>养正中学</t>
+          <t>文海实验学校</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>钱塘区民办第一，优高率近80%</t>
+          <t>钱塘区公办第一</t>
         </is>
       </c>
     </row>
@@ -6661,22 +6661,30 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>文海实验学校</t>
+          <t>杭州养正学校</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>钱塘区公办第一</t>
-        </is>
-      </c>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6689,17 +6697,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>杭州养正学校</t>
+          <t>杭州启成学校</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6709,15 +6717,19 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>杭高教育集团民办</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6730,12 +6742,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>杭州启成学校</t>
+          <t>杭州市下沙中学</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6745,22 +6757,22 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>杭高教育集团民办</t>
+          <t>下沙板块公办</t>
         </is>
       </c>
     </row>
@@ -6775,39 +6787,35 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>杭州市下沙中学</t>
+          <t>杭州市实验外国语学校</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>十二年一贯制</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>168（打9折）</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>下沙板块公办</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6825,27 +6833,27 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>杭州市实验外国语学校</t>
+          <t>杭州市文海中学</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>168（打9折）</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -6861,12 +6869,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>杭州市文海中学</t>
+          <t>杭州市文海启源中学</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6881,12 +6889,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -6902,12 +6910,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>杭州市文海启源中学</t>
+          <t>杭州市文海实验中学</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6920,16 +6928,8 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>杭州市文海实验中学</t>
+          <t>杭州市文海第二实验学校</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6958,11 +6958,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
@@ -6981,7 +6989,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>杭州市文海第二实验学校</t>
+          <t>杭州市钱塘区义蓬中学</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6991,17 +6999,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -7022,7 +7030,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>杭州市钱塘区义蓬中学</t>
+          <t>杭州市钱塘区前进中学</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7037,12 +7045,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -7058,12 +7066,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>杭州市钱塘区前进中学</t>
+          <t>杭州市钱塘区学正中学</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -7078,15 +7086,19 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>钱塘区公办第二</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7099,12 +7111,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>杭州市钱塘区学正中学</t>
+          <t>杭州市钱塘区学正实验学校</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7114,24 +7126,16 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>钱塘区公办第二</t>
-        </is>
-      </c>
+          <t>新办，无毕业生</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7144,12 +7148,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>杭州市钱塘区学正实验学校</t>
+          <t>杭州市钱塘区新湾中学</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7159,16 +7163,24 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>新办，无毕业生</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>钱塘区东部乡镇初中</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7181,12 +7193,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>杭州市钱塘区新湾中学</t>
+          <t>杭州市钱塘区新湾实验学校</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -7196,24 +7208,16 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>钱塘区东部乡镇初中</t>
-        </is>
-      </c>
+          <t>新办，无毕业生</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7226,12 +7230,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>杭州市钱塘区新湾实验学校</t>
+          <t>杭州市钱塘区景苑中学</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7241,13 +7245,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>新办，无毕业生</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -7263,12 +7271,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>杭州市钱塘区景苑中学</t>
+          <t>杭州市钱塘区江海实验学校</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7278,17 +7286,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -7304,12 +7312,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>杭州市钱塘区江海实验学校</t>
+          <t>杭州市钱塘区观澜中学</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7319,17 +7327,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -7345,12 +7353,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>杭州市钱塘区观澜中学</t>
+          <t>杭州市钱塘区金沙湖实验学校</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7360,17 +7368,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -7386,32 +7394,28 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>杭州市钱塘区金沙湖实验学校</t>
+          <t>杭州鼎文学校</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
+          <t>十二年一贯制</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>新办，无毕业生</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -7427,12 +7431,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>杭州鼎文学校</t>
+          <t>钱塘外国语学校</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7440,18 +7444,14 @@
           <t>民办</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>新办，无毕业生</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>首届中考，优高率78.7%</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7459,22 +7459,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>钱塘区</t>
+          <t>萧山区</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>钱塘外国语学校</t>
+          <t>临浦镇中</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -7482,7 +7482,7 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>首届中考，优高率78.7%</t>
+          <t>萧山区南片龙头</t>
         </is>
       </c>
     </row>
@@ -7497,12 +7497,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>临浦镇中</t>
+          <t>党湾初中</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -7515,7 +7515,7 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>萧山区南片龙头</t>
+          <t>萧山东片学校</t>
         </is>
       </c>
     </row>
@@ -7535,20 +7535,24 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>党湾初中</t>
+          <t>杭州学军中学教育集团文渊中学</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>完全中学</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>萧山东片学校</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7572,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>杭州学军中学教育集团文渊中学</t>
+          <t>湘湖未来学校</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -7576,16 +7580,12 @@
           <t>民办</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>完全中学</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>萧山区第一，重高率82.1%，普高率100%</t>
         </is>
       </c>
     </row>
@@ -7600,17 +7600,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>湘湖未来学校</t>
+          <t>瓜沥一中</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7618,7 +7618,7 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>萧山区第一，重高率82.1%，普高率100%</t>
+          <t>萧山东片龙头</t>
         </is>
       </c>
     </row>
@@ -7633,12 +7633,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>瓜沥一中</t>
+          <t>益农初中</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7651,7 +7651,7 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>萧山东片龙头</t>
+          <t>萧山东片学校</t>
         </is>
       </c>
     </row>
@@ -7666,12 +7666,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>益农初中</t>
+          <t>萧山区万向初级中学</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7679,12 +7679,16 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>独立初中</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>萧山东片学校</t>
+          <t>万向集团配套公办初中</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7708,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>萧山区万向初级中学</t>
+          <t>萧山区临浦镇初级中学</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7721,7 +7725,7 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>万向集团配套公办初中</t>
+          <t>临浦镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -7736,12 +7740,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>萧山区临浦镇初级中学</t>
+          <t>萧山区义桥实验学校</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7751,14 +7755,14 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>临浦镇核心公办初中</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -7773,12 +7777,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>萧山区义桥实验学校</t>
+          <t>萧山区党湾镇初级中学</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7788,14 +7792,14 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>党湾镇公办初中</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7814,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>萧山区党湾镇初级中学</t>
+          <t>萧山区北干初级中学</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7832,7 +7836,7 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>党湾镇公办初中</t>
+          <t>北干初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -7847,12 +7851,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>萧山区北干初级中学</t>
+          <t>萧山区回澜初级中学</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7869,7 +7873,7 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>北干初中教育集团核心校</t>
+          <t>回澜初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -7884,12 +7888,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>萧山区回澜初级中学</t>
+          <t>萧山区城南初级中学</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7906,7 +7910,7 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>回澜初中教育集团核心校</t>
+          <t>城南初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7930,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>萧山区城南初级中学</t>
+          <t>萧山区宁围街道初级中学</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7943,7 +7947,7 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>城南初中教育集团核心校</t>
+          <t>宁围街道公办初中</t>
         </is>
       </c>
     </row>
@@ -7963,24 +7967,24 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>萧山区宁围街道初级中学</t>
+          <t>萧山区实验外国语学校</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>宁围街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -8000,24 +8004,24 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>萧山区实验外国语学校</t>
+          <t>萧山区市心实验中学</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>2025年新启用公办初中</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8041,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>萧山区市心实验中学</t>
+          <t>萧山区戴村镇初级中学</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -8054,7 +8058,7 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2025年新启用公办初中</t>
+          <t>戴村镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8078,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>萧山区戴村镇初级中学</t>
+          <t>萧山区所前镇初级中学</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -8091,7 +8095,7 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>戴村镇公办初中</t>
+          <t>所前镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8115,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>萧山区所前镇初级中学</t>
+          <t>萧山区新塘街道初级中学</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -8128,7 +8132,7 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>所前镇公办初中</t>
+          <t>新塘街道公办初中</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8152,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>萧山区新塘街道初级中学</t>
+          <t>萧山区新街初级中学</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8165,7 +8169,7 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>新塘街道公办初中</t>
+          <t>新街镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8189,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>萧山区新街初级中学</t>
+          <t>萧山区河上镇初级中学</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8202,7 +8206,7 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>新街镇核心公办初中</t>
+          <t>河上镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8226,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>萧山区河上镇初级中学</t>
+          <t>萧山区浦阳镇初级中学</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -8239,7 +8243,7 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>河上镇公办初中</t>
+          <t>浦阳镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8263,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>萧山区浦阳镇初级中学</t>
+          <t>萧山区湘湖初级中学</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -8276,7 +8280,7 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>浦阳镇公办初中</t>
+          <t>高桥初中教育集团成员校</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8300,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>萧山区湘湖初级中学</t>
+          <t>萧山区瓜沥镇坎山初级中学</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -8313,7 +8317,7 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>高桥初中教育集团成员校</t>
+          <t>原坎山镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8337,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>萧山区瓜沥镇坎山初级中学</t>
+          <t>萧山区瓜沥镇第一初级中学</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -8350,7 +8354,7 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>原坎山镇公办初中</t>
+          <t>瓜沥镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8374,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>萧山区瓜沥镇第一初级中学</t>
+          <t>萧山区盈丰街道初级中学</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -8387,7 +8391,7 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>瓜沥镇核心公办初中</t>
+          <t>盈丰街道公办初中</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8411,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>萧山区盈丰街道初级中学</t>
+          <t>萧山区红山农场学校</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -8417,14 +8421,14 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>盈丰街道公办初中</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8448,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>萧山区红山农场学校</t>
+          <t>萧山区虎山路初级中学</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -8454,14 +8458,14 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>虎山路初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8485,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>萧山区虎山路初级中学</t>
+          <t>萧山区蜀山中心学校</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -8491,14 +8495,14 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>虎山路初中教育集团核心校</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8522,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>萧山区蜀山中心学校</t>
+          <t>萧山区衙前镇初级中学</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -8528,14 +8532,14 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>衙前镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8559,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>萧山区衙前镇初级中学</t>
+          <t>萧山区贺知章学校</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -8565,14 +8569,14 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>衙前镇公办初中</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8596,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>萧山区贺知章学校</t>
+          <t>萧山区进化镇初级中学</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -8602,14 +8606,14 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>进化镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8628,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>萧山区进化镇初级中学</t>
+          <t>萧山区金山初级中学</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -8646,7 +8650,7 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
-          <t>进化镇公办初中</t>
+          <t>金山初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -8661,12 +8665,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>萧山区金山初级中学</t>
+          <t>萧山区闻堰初级中学</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -8683,7 +8687,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>金山初中教育集团核心校</t>
+          <t>闻堰街道公办初中</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8707,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>萧山区闻堰初级中学</t>
+          <t>萧山区靖江初级中学</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -8720,7 +8724,7 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
-          <t>闻堰街道公办初中</t>
+          <t>靖江街道公办初中</t>
         </is>
       </c>
     </row>
@@ -8735,12 +8739,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>萧山区靖江初级中学</t>
+          <t>萧山区高桥初级中学</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -8757,7 +8761,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>靖江街道公办初中</t>
+          <t>高桥初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -8772,29 +8776,29 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>萧山区高桥初级中学</t>
+          <t>萧山区高桥金帆实验学校</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>高桥初中教育集团核心校</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8813,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>萧山区高桥金帆实验学校</t>
+          <t>萧山实验中学</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -8822,16 +8826,12 @@
           <t>民办</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>萧山区民办</t>
         </is>
       </c>
     </row>
@@ -8846,12 +8846,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>萧山实验中学</t>
+          <t>金帆学校</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -8874,22 +8874,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>萧山区</t>
+          <t>余杭区</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>金帆学校</t>
+          <t>余杭一中实验</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -8897,7 +8897,7 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
-          <t>萧山区民办</t>
+          <t>余杭区公办</t>
         </is>
       </c>
     </row>
@@ -8917,12 +8917,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>余杭一中实验</t>
+          <t>天元公学</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -8930,7 +8930,7 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
-          <t>余杭区公办</t>
+          <t>余杭区第一，杭二教育集团</t>
         </is>
       </c>
     </row>
@@ -8945,17 +8945,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>天元公学</t>
+          <t>未来科技城海创园</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -8963,7 +8963,7 @@
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
-          <t>余杭区第一，杭二教育集团</t>
+          <t>未来科技城公办第一</t>
         </is>
       </c>
     </row>
@@ -8978,25 +8978,29 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>未来科技城海创园</t>
+          <t>杭州市余杭区东方未来学校</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr"/>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>九年一贯制</t>
+        </is>
+      </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>未来科技城公办第一</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9011,12 +9015,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>杭州市余杭区东方未来学校</t>
+          <t>杭州市余杭区东澜外国语学校</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -9029,8 +9033,16 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="I216" t="inlineStr">
         <is>
           <t>含初中部，需摇号</t>
@@ -9053,32 +9065,32 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>杭州市余杭区东澜外国语学校</t>
+          <t>杭州市余杭区中泰中学</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>中泰街道公办初中</t>
         </is>
       </c>
     </row>
@@ -9093,37 +9105,29 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>杭州市余杭区中泰中学</t>
+          <t>杭州市余杭区中泰武术学校</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
-          <t>中泰街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9138,29 +9142,37 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>杭州市余杭区中泰武术学校</t>
+          <t>杭州市余杭区五常中学</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>五常街道公办初中</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9187,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>杭州市余杭区五常中学</t>
+          <t>杭州市余杭区仁和中学</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -9195,17 +9207,17 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>430</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>五常街道公办初中</t>
+          <t>仁和街道公办初中</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9237,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>杭州市余杭区仁和中学</t>
+          <t>杭州市余杭区仓前中学</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -9240,17 +9252,17 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>仁和街道公办初中</t>
+          <t>仓前街道公办初中</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9282,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>杭州市余杭区仓前中学</t>
+          <t>杭州市余杭区南湖实验学校</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -9280,24 +9292,20 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>仓前街道公办初中</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -9310,12 +9318,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>杭州市余杭区南湖实验学校</t>
+          <t>杭州市余杭区太炎中学</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -9325,20 +9333,24 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>940</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>仓前街道核心公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -9351,37 +9363,37 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>杭州市余杭区太炎中学</t>
+          <t>杭州市余杭区安吉路良渚实验学校</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>540</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>仓前街道核心公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9396,37 +9408,37 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>杭州市余杭区安吉路良渚实验学校</t>
+          <t>杭州市余杭区径山中学</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>径山镇公办初中</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9458,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>杭州市余杭区径山中学</t>
+          <t>杭州市余杭区文化村实验学校</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -9456,24 +9468,20 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>径山镇公办初中</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -9486,35 +9494,31 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>杭州市余杭区文化村实验学校</t>
+          <t>杭州市余杭区新明半岛英才学校</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>含初中部，需摇号</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -9527,29 +9531,37 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>杭州市余杭区新明半岛英才学校</t>
+          <t>杭州市余杭区杜甫中学</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>良渚街道公办初中</t>
         </is>
       </c>
     </row>
@@ -9569,34 +9581,30 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>杭州市余杭区杜甫中学</t>
+          <t>杭州市余杭区树兰英才学校（初中部）</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>民办初中</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>良渚街道公办初中</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -9614,30 +9622,34 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>杭州市余杭区树兰英才学校（初中部）</t>
+          <t>杭州市余杭区沈括中学</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>民办初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>未来科技城公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -9650,12 +9662,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>杭州市余杭区沈括中学</t>
+          <t>杭州市余杭区海辰中学</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -9670,12 +9682,12 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -9695,39 +9707,35 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>杭州市余杭区海辰中学</t>
+          <t>杭州市余杭区狄邦文理学校（初中部）</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>民办初中</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>未来科技城公办初中</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -9740,35 +9748,39 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>杭州市余杭区狄邦文理学校（初中部）</t>
+          <t>杭州市余杭区瓶窑第一中学</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>民办初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>瓶窑镇核心公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -9781,12 +9793,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>杭州市余杭区瓶窑第一中学</t>
+          <t>杭州市余杭区百丈中学</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -9799,19 +9811,11 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
-          <t>瓶窑镇核心公办初中</t>
+          <t>百丈镇公办初中</t>
         </is>
       </c>
     </row>
@@ -9826,12 +9830,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>杭州市余杭区百丈中学</t>
+          <t>杭州市余杭区禹航实验学校</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -9841,16 +9845,20 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>百丈镇公办初中</t>
-        </is>
-      </c>
+          <t>公办九年一贯制（内设初中部）</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -9863,35 +9871,39 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>杭州市余杭区禹航实验学校</t>
+          <t>杭州市余杭区绿城育华亲亲学校（初中部）</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>民办初中</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>余杭区民办，普高率92.4%</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -9909,7 +9921,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>杭州市余杭区绿城育华亲亲学校（初中部）</t>
+          <t>杭州市余杭区育海外国语学校</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -9919,22 +9931,22 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>民办初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>余杭区民办，普高率92.4%</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9949,37 +9961,37 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>杭州市余杭区育海外国语学校</t>
+          <t>杭州市余杭区良渚第一中学</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>良渚街道核心公办初中</t>
         </is>
       </c>
     </row>
@@ -9999,7 +10011,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>杭州市余杭区良渚第一中学</t>
+          <t>杭州市余杭区良渚第二中学</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -10014,17 +10026,17 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>790</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>良渚街道核心公办初中</t>
+          <t>良渚街道公办初中</t>
         </is>
       </c>
     </row>
@@ -10039,37 +10051,29 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>杭州市余杭区良渚第二中学</t>
+          <t>杭州市余杭区蒲公英学校</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
-          <t>良渚街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -10084,29 +10088,37 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>杭州市余杭区蒲公英学校</t>
+          <t>杭州市余杭区闲林中学</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>闲林街道核心公办初中</t>
         </is>
       </c>
     </row>
@@ -10121,12 +10133,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>杭州市余杭区闲林中学</t>
+          <t>杭州市余杭区鸬鸟中学</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -10139,19 +10151,11 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
-          <t>闲林街道核心公办初中</t>
+          <t>鸬鸟镇公办初中</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10170,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>杭州市余杭区鸬鸟中学</t>
+          <t>杭州市余杭区黄湖中学</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -10184,11 +10188,19 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>鸬鸟镇公办初中</t>
+          <t>黄湖镇公办初中</t>
         </is>
       </c>
     </row>
@@ -10203,37 +10215,33 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>杭州市余杭区黄湖中学</t>
+          <t>杭州市余杭蔚澜学校</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
-          <t>黄湖镇公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -10248,33 +10256,37 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>杭州市余杭蔚澜学校</t>
+          <t>杭州师范大学附属未来科技城中学</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr"/>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>杭州二中教育集团核心校，未来科技城核心公办</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10306,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>杭州师范大学附属未来科技城中学</t>
+          <t>杭州师范大学附属未来科技城学校</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -10302,24 +10314,12 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
-          <t>杭州二中教育集团核心校，未来科技城核心公办</t>
+          <t>杭师大附属公办</t>
         </is>
       </c>
     </row>
@@ -10334,25 +10334,37 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>杭州师范大学附属未来科技城学校</t>
+          <t>杭州维翰学校</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>杭师大附属公办</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -10367,12 +10379,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>杭州维翰学校</t>
+          <t>杭州绿城亲亲学校</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -10385,16 +10397,8 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>含初中部，需摇号</t>
@@ -10417,7 +10421,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>杭州绿城亲亲学校</t>
+          <t>杭州绿城育华桃花源学校</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -10427,7 +10431,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>十二年一贯制</t>
         </is>
       </c>
       <c r="G249" t="inlineStr"/>
@@ -10449,12 +10453,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>杭州绿城育华桃花源学校</t>
+          <t>杭州绿城育华翡翠城学校</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -10464,11 +10468,19 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr">
         <is>
           <t>含初中部，需摇号</t>
@@ -10486,12 +10498,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>杭州绿城育华翡翠城学校</t>
+          <t>杭州英特外国语学校</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -10506,17 +10518,17 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>含初中部，需摇号，余杭头部民办</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10543,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>杭州英特外国语学校</t>
+          <t>杭州蕙兰未来科技城学校</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -10546,22 +10558,22 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>十二年一贯制</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>含初中部，需摇号，余杭头部民办</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -10576,12 +10588,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>杭州蕙兰未来科技城学校</t>
+          <t>橄榄树学校</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -10589,24 +10601,12 @@
           <t>民办</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>国际化民办</t>
         </is>
       </c>
     </row>
@@ -10621,17 +10621,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>橄榄树学校</t>
+          <t>瓶窑一中</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -10639,7 +10639,7 @@
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
-          <t>国际化民办</t>
+          <t>余杭西部乡镇初中</t>
         </is>
       </c>
     </row>
@@ -10654,12 +10654,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>瓶窑一中</t>
+          <t>良渚一中</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -10672,7 +10672,7 @@
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
-          <t>余杭西部乡镇初中</t>
+          <t>良渚板块公办</t>
         </is>
       </c>
     </row>
@@ -10682,17 +10682,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>余杭区</t>
+          <t>临平区</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>良渚一中</t>
+          <t>临平一中</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -10705,7 +10705,7 @@
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
-          <t>良渚板块公办</t>
+          <t>临平区公办第一</t>
         </is>
       </c>
     </row>
@@ -10720,12 +10720,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>临平一中</t>
+          <t>临平三中</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -10738,7 +10738,7 @@
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
-          <t>临平区公办第一</t>
+          <t>临平城区公办</t>
         </is>
       </c>
     </row>
@@ -10753,12 +10753,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>临平三中</t>
+          <t>临平五中</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>临平五中</t>
+          <t>塘栖二中</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -10804,7 +10804,7 @@
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
-          <t>临平城区公办</t>
+          <t>塘栖板块公办</t>
         </is>
       </c>
     </row>
@@ -10824,20 +10824,32 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>塘栖二中</t>
+          <t>杭州信达外国语学校</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>塘栖板块公办</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -10852,12 +10864,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>杭州信达外国语学校</t>
+          <t>杭州光华外国语学校</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -10872,12 +10884,12 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -10897,37 +10909,37 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>杭州光华外国语学校</t>
+          <t>杭州市临平区临平第一中学</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>780</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>含望梅校区、南汇校区，临平核心公办</t>
         </is>
       </c>
     </row>
@@ -10947,7 +10959,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第一中学</t>
+          <t>杭州市临平区临平第三中学</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -10962,17 +10974,17 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>含望梅校区、南汇校区，临平核心公办</t>
+          <t>含梅堰校区、风荷校区，临平城区公办</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10999,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第三中学</t>
+          <t>杭州市临平区临平第二中学</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -11007,17 +11019,17 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>含梅堰校区、风荷校区，临平城区公办</t>
+          <t>临平城区公办初中</t>
         </is>
       </c>
     </row>
@@ -11032,12 +11044,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第二中学</t>
+          <t>杭州市临平区临平第五中学</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -11052,12 +11064,12 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -11077,12 +11089,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第五中学</t>
+          <t>杭州市临平区乔司中学</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -11097,17 +11109,17 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>临平城区公办初中</t>
+          <t>乔司街道公办初中</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11139,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>杭州市临平区乔司中学</t>
+          <t>杭州市临平区启文中学</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -11142,17 +11154,17 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>乔司街道公办初中</t>
+          <t>临平城区公办初中</t>
         </is>
       </c>
     </row>
@@ -11167,12 +11179,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>杭州市临平区启文中学</t>
+          <t>杭州市临平区启明实验学校</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -11182,24 +11194,20 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>临平城区公办初中</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -11217,7 +11225,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>杭州市临平区启明实验学校</t>
+          <t>杭州市临平区吴昌硕实验学校</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -11227,20 +11235,24 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>含初中部</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -11253,12 +11265,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>杭州市临平区吴昌硕实验学校</t>
+          <t>杭州市临平区塘栖第三中学</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -11268,22 +11280,22 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>660</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>2026年新启用公办初中</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11310,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>杭州市临平区塘栖第三中学</t>
+          <t>杭州市临平区塘栖第二中学</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -11318,17 +11330,17 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2026年新启用公办初中</t>
+          <t>塘栖镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -11343,12 +11355,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>杭州市临平区塘栖第二中学</t>
+          <t>杭州市临平区崇贤中学</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -11363,17 +11375,17 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>塘栖镇核心公办初中</t>
+          <t>崇贤街道公办初中</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11405,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>杭州市临平区崇贤中学</t>
+          <t>杭州市临平区星华实验学校</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -11403,22 +11415,22 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>崇贤街道公办初中</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11450,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>杭州市临平区星华实验学校</t>
+          <t>杭州市临平区星桥中学</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -11448,22 +11460,22 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>430</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>星桥街道公办初中</t>
         </is>
       </c>
     </row>
@@ -11483,7 +11495,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>杭州市临平区星桥中学</t>
+          <t>杭州市临平区永进学校</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -11493,22 +11505,22 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>星桥街道公办初中</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11540,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>杭州市临平区永进学校</t>
+          <t>杭州市临平区沾桥中学</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -11538,22 +11550,22 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>崇贤街道公办初中</t>
         </is>
       </c>
     </row>
@@ -11568,12 +11580,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>杭州市临平区沾桥中学</t>
+          <t>杭州市临平区运河中学</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -11588,17 +11600,17 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>崇贤街道公办初中</t>
+          <t>运河街道公办初中</t>
         </is>
       </c>
     </row>
@@ -11613,37 +11625,29 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>杭州市临平区运河中学</t>
+          <t>杭州市余杭区林苑学校</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
-          <t>运河街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11667,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>杭州市余杭区林苑学校</t>
+          <t>杭州市余杭区育蕾学校运河校区</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -11695,12 +11699,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>杭州市余杭区育蕾学校运河校区</t>
+          <t>杭州树兰实验学校</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -11713,8 +11717,16 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
       <c r="I280" t="inlineStr">
         <is>
           <t>含初中部，需摇号</t>
@@ -11732,12 +11744,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>杭州树兰实验学校</t>
+          <t>杭州橄榄树学校</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -11747,17 +11759,17 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>十二年一贯制</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -11777,37 +11789,25 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>杭州橄榄树学校</t>
+          <t>杭高临平学校</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>杭高教育集团新校</t>
         </is>
       </c>
     </row>
@@ -11817,17 +11817,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>临平区</t>
+          <t>富阳区</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>杭高临平学校</t>
+          <t>场口中学</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -11840,7 +11840,7 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
-          <t>杭高教育集团新校</t>
+          <t>富阳场口板块</t>
         </is>
       </c>
     </row>
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>场口中学</t>
+          <t>富春三中</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -11873,7 +11873,7 @@
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
-          <t>富阳场口板块</t>
+          <t>富阳城区公办</t>
         </is>
       </c>
     </row>
@@ -11888,25 +11888,29 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>富春三中</t>
+          <t>杭州上附外国语学校</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr"/>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>九年一贯制</t>
+        </is>
+      </c>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
-          <t>富阳城区公办</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11930,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>杭州上附外国语学校</t>
+          <t>杭州东吴实验学校</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -11963,26 +11967,22 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>杭州东吴实验学校</t>
+          <t>杭州富阳区高桥中学</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>含初中部，需摇号</t>
-        </is>
-      </c>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>杭州富阳区高桥中学</t>
+          <t>杭州富阳永昌中学</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>杭州富阳永昌中学</t>
+          <t>杭州富阳胥口中学</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>杭州富阳胥口中学</t>
+          <t>杭州富阳里山镇中学</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>杭州富阳里山镇中学</t>
+          <t>杭州市富阳区万市中学</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -12114,7 +12114,11 @@
       </c>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>万市镇公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -12132,7 +12136,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>杭州市富阳区万市中学</t>
+          <t>杭州市富阳区上官乡中学</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -12149,7 +12153,7 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>万市镇公办初中</t>
+          <t>上官乡公办初中</t>
         </is>
       </c>
     </row>
@@ -12164,12 +12168,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>杭州市富阳区上官乡中学</t>
+          <t>杭州市富阳区东洲中学</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -12186,7 +12190,7 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>上官乡公办初中</t>
+          <t>东洲街道公办初中</t>
         </is>
       </c>
     </row>
@@ -12201,12 +12205,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>杭州市富阳区东洲中学</t>
+          <t>杭州市富阳区场口镇中学</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -12223,7 +12227,7 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
-          <t>东洲街道公办初中</t>
+          <t>场口镇公办初中</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12247,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>杭州市富阳区场口镇中学</t>
+          <t>杭州市富阳区大源中学</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -12260,7 +12264,7 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>场口镇公办初中</t>
+          <t>大源镇公办初中</t>
         </is>
       </c>
     </row>
@@ -12275,12 +12279,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>杭州市富阳区大源中学</t>
+          <t>杭州市富阳区富春中学</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -12297,7 +12301,7 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
-          <t>大源镇公办初中</t>
+          <t>城区核心公办初中</t>
         </is>
       </c>
     </row>
@@ -12312,12 +12316,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>杭州市富阳区富春中学</t>
+          <t>杭州市富阳区富春第三中学</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -12354,7 +12358,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>杭州市富阳区富春第三中学</t>
+          <t>杭州市富阳区常安镇中学</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -12371,7 +12375,7 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>城区核心公办初中</t>
+          <t>常安镇公办初中</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12390,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>杭州市富阳区常安镇中学</t>
+          <t>杭州市富阳区新登镇中学</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -12408,7 +12412,7 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>常安镇公办初中</t>
+          <t>新登镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -12423,12 +12427,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>杭州市富阳区新登镇中学</t>
+          <t>杭州市富阳区春建乡中学</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -12445,7 +12449,7 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
-          <t>新登镇核心公办初中</t>
+          <t>春建乡公办初中</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12469,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>杭州市富阳区春建乡中学</t>
+          <t>杭州市富阳区春江中学</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -12482,7 +12486,7 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>春建乡公办初中</t>
+          <t>春江街道公办初中</t>
         </is>
       </c>
     </row>
@@ -12497,29 +12501,29 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>杭州市富阳区春江中学</t>
+          <t>杭州市富阳区永兴学校</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>春江街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -12534,29 +12538,29 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>杭州市富阳区永兴学校</t>
+          <t>杭州市富阳区湖源乡中学</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>湖源乡公办初中</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12580,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>杭州市富阳区湖源乡中学</t>
+          <t>杭州市富阳区灵桥镇中学</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -12593,7 +12597,7 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
-          <t>湖源乡公办初中</t>
+          <t>灵桥镇公办初中</t>
         </is>
       </c>
     </row>
@@ -12613,7 +12617,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>杭州市富阳区灵桥镇中学</t>
+          <t>杭州市富阳区环山中学</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -12630,7 +12634,7 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>灵桥镇公办初中</t>
+          <t>环山乡公办初中</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12654,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>杭州市富阳区环山中学</t>
+          <t>杭州市富阳区贤明中学</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -12667,7 +12671,7 @@
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
-          <t>环山乡公办初中</t>
+          <t>新登镇公办初中</t>
         </is>
       </c>
     </row>
@@ -12682,12 +12686,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>杭州市富阳区贤明中学</t>
+          <t>杭州市富阳区郁达夫中学</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -12704,7 +12708,7 @@
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
-          <t>新登镇公办初中</t>
+          <t>含达夫校区、文豪校区，城区核心公办</t>
         </is>
       </c>
     </row>
@@ -12719,12 +12723,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>杭州市富阳区郁达夫中学</t>
+          <t>杭州市富阳区银湖中学</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -12741,7 +12745,7 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
-          <t>含达夫校区、文豪校区，城区核心公办</t>
+          <t>银湖街道核心公办初中</t>
         </is>
       </c>
     </row>
@@ -12761,7 +12765,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>杭州市富阳区银湖中学</t>
+          <t>杭州市富阳区鹿山中学</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -12778,7 +12782,7 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
-          <t>银湖街道核心公办初中</t>
+          <t>鹿山街道公办初中</t>
         </is>
       </c>
     </row>
@@ -12793,17 +12797,17 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>杭州市富阳区鹿山中学</t>
+          <t>杭州银湖实验中学</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -12814,43 +12818,6 @@
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
-        <is>
-          <t>鹿山街道公办初中</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>310</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>富阳区</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>杭州银湖实验中学</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr">
         <is>
           <t>需摇号，富阳头部民办</t>
         </is>

--- a/杭州9区初中梯队总表_整理版.xlsx
+++ b/杭州9区初中梯队总表_整理版.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J308"/>
+  <dimension ref="A1:J305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5209,8 +5209,16 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>253.658536585366</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>2026年停止招生</t>
@@ -5228,40 +5236,36 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>之江实验中学（民转公）</t>
+          <t>仁和实验学校（初中部）</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>杭州市之江实验中学（民转公）</t>
+          <t>杭州市仁和实验学校（初中部）</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>253.658536585366</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>西湖风景名胜区民办</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5274,34 +5278,42 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>仁和实验学校（初中部）</t>
+          <t>保俶塔实验学校（初中部）</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>杭州市仁和实验学校（初中部）</t>
+          <t>杭州市保俶塔实验学校（初中部）</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>419.512195121951</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>西湖风景名胜区民办</t>
+          <t>保俶塔系本部</t>
         </is>
       </c>
     </row>
@@ -5316,17 +5328,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>保俶塔实验学校（初中部）</t>
+          <t>保俶塔申花实验</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>杭州市保俶塔实验学校（初中部）</t>
+          <t>杭州市保俶塔申花实验学校（初中部）</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5339,13 +5351,17 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>保俶塔系本部</t>
-        </is>
-      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5363,35 +5379,39 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>保俶塔实验学校（本部）</t>
+          <t>公益中学</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>杭州市保俶塔实验学校（本部）</t>
+          <t>杭州市公益中学</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>公办（民转公）</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>419.512195121951</t>
+          <t>400</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr"/>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026年正常招生，需摇号</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5404,17 +5424,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>保俶塔申花实验</t>
+          <t>十三中教育集团（总校）嘉绿苑中学</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>杭州市保俶塔申花实验学校（初中部）</t>
+          <t>十三中教育集团（总校）嘉绿苑中学</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5424,20 +5444,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>443.90243902439</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr"/>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>十三中教育集团</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5450,22 +5474,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>公益中学</t>
+          <t>十三中教育集团（总校）杭十三中</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>杭州市公益中学</t>
+          <t>十三中教育集团（总校）杭十三中</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>公办（民转公）</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -5473,13 +5497,17 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>2026年正常招生，需摇号</t>
-        </is>
-      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5492,17 +5520,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>公益中学（民转公）</t>
+          <t>十五中教育集团（总校）崇德校区</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>杭州市公益中学（民转公）</t>
+          <t>十五中教育集团（总校）崇德校区</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5512,17 +5540,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>418</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -5538,17 +5566,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>十三中教育集团（总校）嘉绿苑中学</t>
+          <t>十五中教育集团（总校）浙大附初校区</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>十三中教育集团（总校）嘉绿苑中学</t>
+          <t>十五中教育集团（总校）浙大附初校区</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5561,21 +5589,9 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>443.90243902439</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>十三中教育集团</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5588,17 +5604,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>十三中教育集团（总校）杭十三中</t>
+          <t>吉鸿中学</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>十三中教育集团（总校）杭十三中</t>
+          <t>杭州市吉鸿中学</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5608,17 +5624,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>243</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -5634,17 +5650,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>十五中教育集团（总校）崇德校区</t>
+          <t>周浦中学</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>十五中教育集团（总校）崇德校区</t>
+          <t>杭州市周浦中学</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5659,15 +5675,19 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>324</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>西湖区乡镇初中</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5680,17 +5700,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>十五中教育集团（总校）浙大附初校区</t>
+          <t>弘益中学</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>十五中教育集团（总校）浙大附初校区</t>
+          <t>杭州市弘益中学</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5703,8 +5723,16 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>448.780487804878</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
@@ -5718,17 +5746,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>吉鸿中学</t>
+          <t>文溪中学</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>杭州市吉鸿中学</t>
+          <t>杭州市文溪中学</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5738,17 +5766,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -5764,17 +5792,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>周浦中学</t>
+          <t>文理中学</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>杭州市周浦中学</t>
+          <t>杭州市文理中学</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5784,24 +5812,20 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>400</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>西湖区乡镇初中</t>
-        </is>
-      </c>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5814,37 +5838,37 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>弘益中学</t>
+          <t>杭州云谷学校（初中部）</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>杭州市弘益中学</t>
+          <t>杭州云谷学校（初中部）</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>448.780487804878</t>
+          <t>暂无公开精确数据</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -5860,17 +5884,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>文溪中学</t>
+          <t>杭州外国语学校</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>杭州市文溪中学</t>
+          <t>杭州外国语学校</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5878,22 +5902,14 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>全省招生，大量保送，不参与中考排名</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5906,40 +5922,44 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>文理中学</t>
+          <t>杭州绿城育华学校（初中部）</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>杭州市文理中学</t>
+          <t>杭州绿城育华学校（初中部）</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>228</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>杭州老牌民办</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5952,22 +5972,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>杭州云谷学校（初中部）</t>
+          <t>浙江工业大学附属实验学校（初中部）</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>杭州云谷学校（初中部）</t>
+          <t>浙江工业大学附属实验学校（初中部）</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5977,12 +5997,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>暂无公开精确数据</t>
+          <t>292.682926829268</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -5998,17 +6018,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>杭州外国语学校</t>
+          <t>第一实验学校（初中部）</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>杭州外国语学校</t>
+          <t>杭州市西湖第一实验学校（初中部）</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6016,14 +6036,22 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>全省招生，大量保送，不参与中考排名</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>暂无公开精确数据</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6036,44 +6064,40 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>杭州绿城育华学校（初中部）</t>
+          <t>第十五中学教育集团・浙大附初校区</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>杭州绿城育华学校（初中部）</t>
+          <t>杭州市第十五中学教育集团・浙大附初校区</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>暂无公开精确数据</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>杭州老牌民办</t>
-        </is>
-      </c>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6086,17 +6110,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>浙江工业大学附属实验学校（初中部）</t>
+          <t>紫金港中学</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>浙江工业大学附属实验学校（初中部）</t>
+          <t>杭州市紫金港中学</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6106,20 +6130,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>292.682926829268</t>
+          <t>424.390243902439</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr"/>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>西湖区公办黑马，今年大爆发</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -6132,17 +6160,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>第一实验学校（初中部）</t>
+          <t>翠苑中学</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>杭州市西湖第一实验学校（初中部）</t>
+          <t>杭州市翠苑中学（翠苑校区、文华校区）</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6152,17 +6180,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>公办独立初中</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>暂无公开精确数据</t>
+          <t>356.09756097561</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6178,17 +6206,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>第十五中学教育集团・浙大附初校区</t>
+          <t>翠苑中学文华校区</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>杭州市第十五中学教育集团・浙大附初校区</t>
+          <t>翠苑中学文华校区</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6198,19 +6226,11 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>暂无公开精确数据</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
@@ -6224,17 +6244,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>紫金港中学</t>
+          <t>翠苑中学翠苑校区</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>杭州市紫金港中学</t>
+          <t>翠苑中学翠苑校区</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6247,21 +6267,9 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>424.390243902439</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>西湖区公办黑马，今年大爆发</t>
-        </is>
-      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6274,17 +6282,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>翠苑中学</t>
+          <t>袁浦中学</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>杭州市翠苑中学（翠苑校区、文华校区）</t>
+          <t>杭州市袁浦中学</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6294,20 +6302,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>356.09756097561</t>
+          <t>619.512195121951</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr"/>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>西湖区乡镇初中</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6320,31 +6332,39 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>翠苑中学文华校区</t>
+          <t>西子实验学校（初中部）</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>翠苑中学文华校区</t>
+          <t>杭州市西子实验学校（初中部）</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+          <t>十二年一贯制</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>暂无公开精确数据</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
@@ -6358,17 +6378,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>翠苑中学翠苑校区</t>
+          <t>西溪中学</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>翠苑中学翠苑校区</t>
+          <t>杭州市西溪中学</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6381,9 +6401,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>517.073170731707</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>西湖区公办第二梯队</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6396,17 +6428,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>袁浦中学</t>
+          <t>西溪实验学校</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>杭州市袁浦中学</t>
+          <t>杭州市西溪实验学校</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6416,24 +6448,20 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>619.512195121951</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>西湖区乡镇初中</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6441,22 +6469,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>西湖区</t>
+          <t>滨江区</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>西子实验学校（初中部）</t>
+          <t>杭州上海世界外国语学校</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>杭州市西子实验学校（初中部）</t>
+          <t>杭州上海世界外国语学校</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6469,16 +6497,8 @@
           <t>十二年一贯制</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>暂无公开精确数据</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
@@ -6487,7 +6507,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>西湖区</t>
+          <t>滨江区</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6497,12 +6517,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>西溪中学</t>
+          <t>杭州二中滨江校区初中部</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>杭州市西溪中学</t>
+          <t>杭州二中滨江校区初中部</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6510,24 +6530,12 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>517.073170731707</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>西湖区公办第二梯队</t>
+          <t>杭二嫡系初中</t>
         </is>
       </c>
     </row>
@@ -6537,45 +6545,49 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>西湖区</t>
+          <t>滨江区</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>西溪实验学校</t>
+          <t>杭州二中白马湖学校（初中部）</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>杭州市西溪实验学校</t>
+          <t>杭州二中白马湖学校（初中部）</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>公办（民转公）</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>275</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2026年正常招生，需摇号</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6588,31 +6600,39 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>杭州上海世界外国语学校</t>
+          <t>杭州二中附属第一学校</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>杭州上海世界外国语学校</t>
+          <t>杭州二中附属第一学校</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
@@ -6626,32 +6646,32 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>杭州二中滨江校区初中部</t>
+          <t>杭州国际学校</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>杭州二中滨江校区初中部</t>
+          <t>杭州国际学校</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr"/>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>十二年一贯制</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>杭二嫡系初中</t>
-        </is>
-      </c>
+      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6664,22 +6684,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>杭州二中白马湖学校（初中部）</t>
+          <t>杭州奥体实验学校</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>杭州二中白马湖学校（初中部）</t>
+          <t>杭州奥体实验学校</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>公办（民转公）</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -6687,21 +6707,9 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>2026年正常招生，需摇号</t>
-        </is>
-      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6714,40 +6722,36 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>杭州二中附属第一学校</t>
+          <t>杭州学军中学教育集团文渊中学</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>杭州二中附属第一学校</t>
+          <t>杭州学军中学教育集团文渊中学</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr"/>
+          <t>完全中学</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>含初中、高中</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6760,32 +6764,44 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>杭州国际学校</t>
+          <t>杭州江南实验学校</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>杭州国际学校</t>
+          <t>杭州江南实验学校</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>滨江公办老牌强校</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6798,17 +6814,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州奥体实验学校</t>
+          <t>杭州湖畔学校</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>杭州奥体实验学校</t>
+          <t>杭州湖畔学校</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6821,8 +6837,16 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
@@ -6836,17 +6860,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>杭州学军中学教育集团文渊中学</t>
+          <t>杭州滨兰实验学校（初中部）</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>杭州学军中学教育集团文渊中学</t>
+          <t>杭州滨兰实验学校（初中部）</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6856,14 +6880,22 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>完全中学</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>含初中、高中</t>
+          <t>滨江区第二，优高率91%全市前列</t>
         </is>
       </c>
     </row>
@@ -6878,17 +6910,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>杭州江南实验学校</t>
+          <t>杭州高级中学附属滨江中学</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>杭州江南实验学校</t>
+          <t>杭州高级中学附属滨江中学</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6898,24 +6930,20 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>滨江公办老牌强校</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6928,17 +6956,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>杭州湖畔学校</t>
+          <t>浙江省杭州滨兴学校</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>杭州湖畔学校</t>
+          <t>浙江省杭州滨兴学校</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6953,12 +6981,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
@@ -6974,42 +7002,42 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>杭州滨兰实验学校（初中部）</t>
+          <t>浙江省杭州高新实验学校</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>杭州滨兰实验学校（初中部）</t>
+          <t>浙江省杭州高新实验学校</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>149</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>滨江区第二，优高率91%全市前列</t>
+          <t>滨江区公办第一</t>
         </is>
       </c>
     </row>
@@ -7024,17 +7052,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>杭州高级中学附属滨江中学</t>
+          <t>浦沿中学</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>杭州高级中学附属滨江中学</t>
+          <t>杭州市浦沿中学</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7049,15 +7077,19 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr"/>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>滨江公办普通校</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -7075,12 +7107,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>浙江省杭州滨兴学校</t>
+          <t>滨和中学</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>浙江省杭州滨兴学校</t>
+          <t>杭州市滨和中学</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7090,20 +7122,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>331</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr"/>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>（滨和教育集团）</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7116,17 +7152,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>浙江省杭州高新实验学校</t>
+          <t>滨文中学</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>浙江省杭州高新实验学校</t>
+          <t>杭州市滨文中学</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7136,24 +7172,20 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>333</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>滨江区公办第一</t>
-        </is>
-      </c>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -7166,17 +7198,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>浦沿中学</t>
+          <t>硅谷中学</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>杭州市浦沿中学</t>
+          <t>杭州市硅谷中学</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7191,19 +7223,15 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>滨江公办普通校</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7221,12 +7249,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>滨和中学</t>
+          <t>竺可桢学校</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>杭州市滨和中学</t>
+          <t>杭州市竺可桢学校</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7241,19 +7269,15 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>（滨和教育集团）</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7271,12 +7295,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>滨文中学</t>
+          <t>西兴中学</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>杭州市滨文中学</t>
+          <t>杭州市西兴中学</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7291,15 +7315,19 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>280</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr"/>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>（滨和教育集团）</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7312,17 +7340,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>硅谷中学</t>
+          <t>钱塘湾初级中学</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>杭州市硅谷中学</t>
+          <t>杭州市钱塘湾初级中学</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7335,16 +7363,8 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
@@ -7363,12 +7383,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>竺可桢学校</t>
+          <t>长河中学</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>杭州市竺可桢学校</t>
+          <t>杭州市长河中学</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7383,15 +7403,19 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>434</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>滨江公办普通校</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7404,17 +7428,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>西兴中学</t>
+          <t>闻涛中学</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>杭州市西兴中学</t>
+          <t>杭州市闻涛中学</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7429,17 +7453,17 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>514</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>（滨和教育集团）</t>
+          <t>滨江公办第二梯队</t>
         </is>
       </c>
     </row>
@@ -7449,22 +7473,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>滨江区</t>
+          <t>钱塘区</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>钱塘湾初级中学</t>
+          <t>下沙中学</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>杭州市钱塘湾初级中学</t>
+          <t>杭州市下沙中学</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7477,9 +7501,21 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>下沙板块公办</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7487,22 +7523,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>滨江区</t>
+          <t>钱塘区</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>长河中学</t>
+          <t>临江一中</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>杭州市长河中学</t>
+          <t>临江一中</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7510,24 +7546,12 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>滨江公办普通校</t>
+          <t>钱塘区东部乡镇初中</t>
         </is>
       </c>
     </row>
@@ -7537,22 +7561,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>滨江区</t>
+          <t>钱塘区</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>闻涛中学</t>
+          <t>义蓬中学</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>杭州市闻涛中学</t>
+          <t>杭州市钱塘区义蓬中学</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7567,19 +7591,15 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>620</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>滨江公办第二梯队</t>
-        </is>
-      </c>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7592,17 +7612,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>下沙中学</t>
+          <t>前进中学</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>杭州市下沙中学</t>
+          <t>杭州市钱塘区前进中学</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7617,19 +7637,15 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>240</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>下沙板块公办</t>
-        </is>
-      </c>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7642,17 +7658,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>临江一中</t>
+          <t>学正中学</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>临江一中</t>
+          <t>杭州市钱塘区学正中学</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7660,12 +7676,24 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>钱塘区东部乡镇初中</t>
+          <t>钱塘区公办第二</t>
         </is>
       </c>
     </row>
@@ -7680,17 +7708,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>义蓬中学</t>
+          <t>学正实验学校</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>杭州市钱塘区义蓬中学</t>
+          <t>杭州市钱塘区学正实验学校</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7700,17 +7728,13 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>新办，无毕业生</t>
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
@@ -7726,17 +7750,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>前进中学</t>
+          <t>文海中学</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>杭州市钱塘区前进中学</t>
+          <t>杭州市文海中学</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7751,12 +7775,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>510</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J161" t="inlineStr"/>
@@ -7772,17 +7796,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>学正中学</t>
+          <t>文海启源中学</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>杭州市钱塘区学正中学</t>
+          <t>杭州市文海启源中学</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7797,19 +7821,15 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>534</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>钱塘区公办第二</t>
-        </is>
-      </c>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7822,17 +7842,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>学正实验学校</t>
+          <t>文海实验中学</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>杭州市钱塘区学正实验学校</t>
+          <t>杭州市文海实验中学</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7842,16 +7862,16 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>新办，无毕业生</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>钱塘区公办第一</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7864,17 +7884,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>文海中学</t>
+          <t>文海实验中学（河庄）</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>杭州市文海中学</t>
+          <t>杭州市文海实验中学（河庄）</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7887,16 +7907,8 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
@@ -7910,17 +7922,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>文海启源中学</t>
+          <t>文海第二实验学校</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>杭州市文海启源中学</t>
+          <t>杭州市文海第二实验学校</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7930,17 +7942,17 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>234</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
@@ -7956,17 +7968,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>文海实验中学</t>
+          <t>新湾中学</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>杭州市文海实验中学</t>
+          <t>杭州市钱塘区新湾中学</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7979,11 +7991,19 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>钱塘区公办第一</t>
+          <t>钱塘区东部乡镇初中</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8023,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>文海实验中学（河庄）</t>
+          <t>新湾实验学校</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>杭州市文海实验中学（河庄）</t>
+          <t>杭州市钱塘区新湾实验学校</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8018,11 +8038,15 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>新办，无毕业生</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
@@ -8036,17 +8060,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>文海第二实验学校</t>
+          <t>景苑中学</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>杭州市文海第二实验学校</t>
+          <t>杭州市钱塘区景苑中学</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8056,17 +8080,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J168" t="inlineStr"/>
@@ -8082,42 +8106,42 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>新湾中学</t>
+          <t>杭州养正学校</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>杭州市钱塘区新湾中学</t>
+          <t>杭州养正学校</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>348</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>钱塘区东部乡镇初中</t>
+          <t>钱塘区民办第一，优高率近80%</t>
         </is>
       </c>
     </row>
@@ -8132,17 +8156,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>新湾实验学校</t>
+          <t>杭州启成学校</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>杭州市钱塘区新湾实验学校</t>
+          <t>杭州启成学校</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8155,13 +8179,21 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>新办，无毕业生</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>杭高教育集团民办</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8174,37 +8206,37 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>景苑中学</t>
+          <t>杭州市实验外国语学校</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>杭州市钱塘区景苑中学</t>
+          <t>杭州市实验外国语学校</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>十二年一贯制</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>168（打9折）</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
@@ -8220,17 +8252,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>杭州养正学校</t>
+          <t>杭州鼎文学校</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>杭州养正学校</t>
+          <t>杭州鼎文学校</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8240,24 +8272,16 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
+          <t>十二年一贯制</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>钱塘区民办第一，优高率近80%</t>
-        </is>
-      </c>
+          <t>新办，无毕业生</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8270,17 +8294,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>杭州启成学校</t>
+          <t>江海实验学校</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>杭州启成学校</t>
+          <t>杭州市钱塘区江海实验学校</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8295,19 +8319,15 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>杭高教育集团民办</t>
-        </is>
-      </c>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -8325,32 +8345,32 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>杭州市实验外国语学校</t>
+          <t>观澜中学</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>杭州市实验外国语学校</t>
+          <t>杭州市钱塘区观澜中学</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>168（打9折）</t>
+          <t>380</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J174" t="inlineStr"/>
@@ -8366,33 +8386,37 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>杭州鼎文学校</t>
+          <t>金沙湖实验学校</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>杭州鼎文学校</t>
+          <t>杭州市钱塘区金沙湖实验学校</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>新办，无毕业生</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
@@ -8413,35 +8437,27 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>江海实验学校</t>
+          <t>钱塘外国语学校</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>杭州市钱塘区江海实验学校</t>
+          <t>钱塘外国语学校</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>首届中考，优高率78.7%</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8449,22 +8465,22 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>钱塘区</t>
+          <t>萧山区</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>观澜中学</t>
+          <t>万向初级中学</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>杭州市钱塘区观澜中学</t>
+          <t>萧山区万向初级中学</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8477,17 +8493,13 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>万向集团配套公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8495,22 +8507,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>钱塘区</t>
+          <t>萧山区</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>金沙湖实验学校</t>
+          <t>临浦镇初级中学</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>杭州市钱塘区金沙湖实验学校</t>
+          <t>萧山区临浦镇初级中学</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8520,20 +8532,16 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>临浦镇核心公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8541,35 +8549,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>钱塘区</t>
+          <t>萧山区</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>钱塘外国语学校</t>
+          <t>义桥实验</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>钱塘外国语学校</t>
+          <t>萧山区义桥实验学校</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr"/>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>九年一贯制</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>首届中考，优高率78.7%</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -8584,17 +8596,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>万向初级中学</t>
+          <t>党湾镇初级中学</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>萧山区万向初级中学</t>
+          <t>萧山区党湾镇初级中学</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8611,7 +8623,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>万向集团配套公办初中</t>
+          <t>党湾镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8638,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>临浦镇初级中学</t>
+          <t>北干初级中学</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>萧山区临浦镇初级中学</t>
+          <t>萧山区北干初级中学</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8653,7 +8665,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>临浦镇核心公办初中</t>
+          <t>北干初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -8668,17 +8680,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>义桥实验</t>
+          <t>回澜初级中学</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>萧山区义桥实验学校</t>
+          <t>萧山区回澜初级中学</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8688,14 +8700,14 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>回澜初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -8710,17 +8722,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>党湾镇初级中学</t>
+          <t>城南初级中学</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>萧山区党湾镇初级中学</t>
+          <t>萧山区城南初级中学</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8737,7 +8749,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>党湾镇公办初中</t>
+          <t>城南初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -8752,17 +8764,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>北干初级中学</t>
+          <t>宁围街道初级中学</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>萧山区北干初级中学</t>
+          <t>萧山区宁围街道初级中学</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8779,7 +8791,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>北干初中教育集团核心校</t>
+          <t>宁围街道公办初中</t>
         </is>
       </c>
     </row>
@@ -8794,17 +8806,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>回澜初级中学</t>
+          <t>市心实验中学</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>萧山区回澜初级中学</t>
+          <t>萧山区市心实验中学</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8821,7 +8833,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>回澜初中教育集团核心校</t>
+          <t>2025年新启用公办初中</t>
         </is>
       </c>
     </row>
@@ -8841,12 +8853,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>城南初级中学</t>
+          <t>戴村镇初级中学</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>萧山区城南初级中学</t>
+          <t>萧山区戴村镇初级中学</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8863,7 +8875,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>城南初中教育集团核心校</t>
+          <t>戴村镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8883,12 +8895,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>宁围街道初级中学</t>
+          <t>所前镇初级中学</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>萧山区宁围街道初级中学</t>
+          <t>萧山区所前镇初级中学</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8905,7 +8917,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>宁围街道公办初中</t>
+          <t>所前镇公办初中</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8937,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>市心实验中学</t>
+          <t>新塘街道初级中学</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>萧山区市心实验中学</t>
+          <t>萧山区新塘街道初级中学</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8947,7 +8959,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2025年新启用公办初中</t>
+          <t>新塘街道公办初中</t>
         </is>
       </c>
     </row>
@@ -8967,12 +8979,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>戴村镇初级中学</t>
+          <t>新街初级中学</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>萧山区戴村镇初级中学</t>
+          <t>萧山区新街初级中学</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8989,7 +9001,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>戴村镇公办初中</t>
+          <t>新街镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -9004,34 +9016,34 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>所前镇初级中学</t>
+          <t>杭州学军中学教育集团文渊中学</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>萧山区所前镇初级中学</t>
+          <t>杭州学军中学教育集团文渊中学</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>完全中学</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>所前镇公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9051,12 +9063,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>新塘街道初级中学</t>
+          <t>河上镇初级中学</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>萧山区新塘街道初级中学</t>
+          <t>萧山区河上镇初级中学</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -9073,7 +9085,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>新塘街道公办初中</t>
+          <t>河上镇公办初中</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9105,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>新街初级中学</t>
+          <t>浦阳镇初级中学</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>萧山区新街初级中学</t>
+          <t>萧山区浦阳镇初级中学</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -9115,7 +9127,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>新街镇核心公办初中</t>
+          <t>浦阳镇公办初中</t>
         </is>
       </c>
     </row>
@@ -9130,34 +9142,34 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>杭州学军中学教育集团文渊中学</t>
+          <t>湘湖初级中学</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>杭州学军中学教育集团文渊中学</t>
+          <t>萧山区湘湖初级中学</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>完全中学</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>高桥初中教育集团成员校</t>
         </is>
       </c>
     </row>
@@ -9172,34 +9184,30 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>河上镇初级中学</t>
+          <t>湘湖未来学校</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>萧山区河上镇初级中学</t>
+          <t>湘湖未来学校</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>河上镇公办初中</t>
+          <t>萧山区第一，重高率82.1%，普高率100%</t>
         </is>
       </c>
     </row>
@@ -9214,17 +9222,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>浦阳镇初级中学</t>
+          <t>瓜沥一中</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>萧山区浦阳镇初级中学</t>
+          <t>萧山区瓜沥镇第一初级中学</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -9241,7 +9249,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>浦阳镇公办初中</t>
+          <t>瓜沥镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9269,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>湘湖初级中学</t>
+          <t>瓜沥镇坎山初级中学</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>萧山区湘湖初级中学</t>
+          <t>萧山区瓜沥镇坎山初级中学</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9283,7 +9291,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>高桥初中教育集团成员校</t>
+          <t>原坎山镇公办初中</t>
         </is>
       </c>
     </row>
@@ -9298,30 +9306,34 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>湘湖未来学校</t>
+          <t>盈丰街道初级中学</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>湘湖未来学校</t>
+          <t>萧山区盈丰街道初级中学</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr"/>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>独立初中</t>
+        </is>
+      </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>萧山区第一，重高率82.1%，普高率100%</t>
+          <t>盈丰街道公办初中</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9353,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>瓜沥一中</t>
+          <t>益农初中</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>萧山区瓜沥镇第一初级中学</t>
+          <t>益农初中</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -9354,16 +9366,12 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>瓜沥镇核心公办初中</t>
+          <t>萧山东片学校</t>
         </is>
       </c>
     </row>
@@ -9383,12 +9391,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>瓜沥镇坎山初级中学</t>
+          <t>红山农场学校</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>萧山区瓜沥镇坎山初级中学</t>
+          <t>萧山区红山农场学校</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -9398,14 +9406,14 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>原坎山镇公办初中</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -9425,29 +9433,29 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>盈丰街道初级中学</t>
+          <t>萧山区实验外国语学校</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>萧山区盈丰街道初级中学</t>
+          <t>萧山区实验外国语学校</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>盈丰街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9462,22 +9470,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>益农初中</t>
+          <t>萧山实验中学</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>益农初中</t>
+          <t>萧山实验中学</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G201" t="inlineStr"/>
@@ -9485,7 +9493,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>萧山东片学校</t>
+          <t>萧山区民办</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9513,12 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>红山农场学校</t>
+          <t>虎山路初级中学</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>萧山区红山农场学校</t>
+          <t>萧山区虎山路初级中学</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -9520,14 +9528,14 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>虎山路初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -9547,17 +9555,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>萧山区实验外国语学校</t>
+          <t>蜀山中心学校</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>萧山区实验外国语学校</t>
+          <t>萧山区蜀山中心学校</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -9569,7 +9577,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -9584,30 +9592,34 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>萧山实验中学</t>
+          <t>衙前镇初级中学</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>萧山实验中学</t>
+          <t>萧山区衙前镇初级中学</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr"/>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>独立初中</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>萧山区民办</t>
+          <t>衙前镇公办初中</t>
         </is>
       </c>
     </row>
@@ -9627,12 +9639,12 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>虎山路初级中学</t>
+          <t>贺知章学校</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>萧山区虎山路初级中学</t>
+          <t>萧山区贺知章学校</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -9642,14 +9654,14 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>虎山路初中教育集团核心校</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -9669,12 +9681,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>蜀山中心学校</t>
+          <t>进化镇初级中学</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>萧山区蜀山中心学校</t>
+          <t>萧山区进化镇初级中学</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -9684,14 +9696,14 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>进化镇公办初中</t>
         </is>
       </c>
     </row>
@@ -9706,17 +9718,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>衙前镇初级中学</t>
+          <t>金山初级中学</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>萧山区衙前镇初级中学</t>
+          <t>萧山区金山初级中学</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -9733,7 +9745,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>衙前镇公办初中</t>
+          <t>金山初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -9753,12 +9765,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>贺知章学校</t>
+          <t>闻堰初级中学</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>萧山区贺知章学校</t>
+          <t>萧山区闻堰初级中学</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9768,14 +9780,14 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>闻堰街道公办初中</t>
         </is>
       </c>
     </row>
@@ -9795,12 +9807,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>进化镇初级中学</t>
+          <t>靖江初级中学</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>萧山区进化镇初级中学</t>
+          <t>萧山区靖江初级中学</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9817,7 +9829,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>进化镇公办初中</t>
+          <t>靖江街道公办初中</t>
         </is>
       </c>
     </row>
@@ -9837,12 +9849,12 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>金山初级中学</t>
+          <t>高桥初级中学</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>萧山区金山初级中学</t>
+          <t>萧山区高桥初级中学</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9859,7 +9871,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>金山初中教育集团核心校</t>
+          <t>高桥初中教育集团核心校</t>
         </is>
       </c>
     </row>
@@ -9874,34 +9886,34 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>闻堰初级中学</t>
+          <t>高桥金帆实验学校</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>萧山区闻堰初级中学</t>
+          <t>萧山区高桥金帆实验学校</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>闻堰街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9923,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>萧山区</t>
+          <t>余杭区</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9921,29 +9933,29 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>靖江初级中学</t>
+          <t>东方未来学校</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>萧山区靖江初级中学</t>
+          <t>杭州市余杭区东方未来学校</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>靖江街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9953,39 +9965,47 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>萧山区</t>
+          <t>余杭区</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>高桥初级中学</t>
+          <t>东澜外国语学校</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>萧山区高桥初级中学</t>
+          <t>杭州市余杭区东澜外国语学校</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>高桥初中教育集团核心校</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -9995,39 +10015,47 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>萧山区</t>
+          <t>余杭区</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>高桥金帆实验学校</t>
+          <t>中泰中学</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>萧山区高桥金帆实验学校</t>
+          <t>杭州市余杭区中泰中学</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>中泰街道公办初中</t>
         </is>
       </c>
     </row>
@@ -10047,12 +10075,12 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>东方未来学校</t>
+          <t>中泰武术学校</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>杭州市余杭区东方未来学校</t>
+          <t>杭州市余杭区中泰武术学校</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -10084,42 +10112,42 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>东澜外国语学校</t>
+          <t>五常中学</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>杭州市余杭区东澜外国语学校</t>
+          <t>杭州市余杭区五常中学</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>403</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>五常街道公办初中</t>
         </is>
       </c>
     </row>
@@ -10139,12 +10167,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>中泰中学</t>
+          <t>仁和中学</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>杭州市余杭区中泰中学</t>
+          <t>杭州市余杭区仁和中学</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -10159,17 +10187,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>430</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>中泰街道公办初中</t>
+          <t>仁和街道公办初中</t>
         </is>
       </c>
     </row>
@@ -10184,34 +10212,42 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>中泰武术学校</t>
+          <t>仓前中学</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>杭州市余杭区中泰武术学校</t>
+          <t>杭州市余杭区仓前中学</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>仓前街道公办初中</t>
         </is>
       </c>
     </row>
@@ -10226,17 +10262,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>五常中学</t>
+          <t>余杭一中实验</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>杭州市余杭区五常中学</t>
+          <t>余杭一中实验</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -10244,24 +10280,12 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t>五常街道公办初中</t>
+          <t>余杭区公办</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10305,12 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>仁和中学</t>
+          <t>南湖实验学校</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>杭州市余杭区仁和中学</t>
+          <t>杭州市余杭区南湖实验学校</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -10296,24 +10320,20 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>470</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>仁和街道公办初中</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -10326,42 +10346,30 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>仓前中学</t>
+          <t>天元公学</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>杭州市余杭区仓前中学</t>
+          <t>天元公学</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
+          <t>民办</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>仓前街道公办初中</t>
+          <t>余杭区第一，杭二教育集团</t>
         </is>
       </c>
     </row>
@@ -10376,17 +10384,17 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>余杭一中实验</t>
+          <t>太炎中学</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>余杭一中实验</t>
+          <t>杭州市余杭区太炎中学</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -10394,12 +10402,24 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>余杭区公办</t>
+          <t>仓前街道核心公办初中</t>
         </is>
       </c>
     </row>
@@ -10419,35 +10439,39 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>南湖实验学校</t>
+          <t>安吉路良渚实验学校</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>杭州市余杭区南湖实验学校</t>
+          <t>杭州市余杭区安吉路良渚实验学校</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>540</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr"/>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>含初中部，需摇号</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10460,30 +10484,42 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>天元公学</t>
+          <t>径山中学</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>天元公学</t>
+          <t>杭州市余杭区径山中学</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>余杭区第一，杭二教育集团</t>
+          <t>径山镇公办初中</t>
         </is>
       </c>
     </row>
@@ -10498,17 +10534,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>太炎中学</t>
+          <t>文化村实验学校</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>杭州市余杭区太炎中学</t>
+          <t>杭州市余杭区文化村实验学校</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -10518,24 +10554,20 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>240</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>仓前街道核心公办初中</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -10548,17 +10580,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>安吉路良渚实验学校</t>
+          <t>新明半岛英才学校</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>杭州市余杭区安吉路良渚实验学校</t>
+          <t>杭州市余杭区新明半岛英才学校</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -10571,16 +10603,8 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>含初中部，需摇号</t>
@@ -10598,17 +10622,17 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>径山中学</t>
+          <t>未来科技城海创园</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>杭州市余杭区径山中学</t>
+          <t>未来科技城海创园</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -10616,24 +10640,12 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>径山镇公办初中</t>
+          <t>未来科技城公办第一</t>
         </is>
       </c>
     </row>
@@ -10653,12 +10665,12 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>文化村实验学校</t>
+          <t>杜甫中学</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>杭州市余杭区文化村实验学校</t>
+          <t>杭州市余杭区杜甫中学</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -10668,20 +10680,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>310</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>良渚街道公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -10694,34 +10710,34 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>新明半岛英才学校</t>
+          <t>杭州师范大学附属未来科技城中学</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>杭州市余杭区新明半岛英才学校</t>
+          <t>杭州师范大学附属未来科技城中学</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>杭州二中教育集团核心校，未来科技城核心公办</t>
         </is>
       </c>
     </row>
@@ -10736,17 +10752,17 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>未来科技城海创园</t>
+          <t>杭州师范大学附属未来科技城中学（杭州二中教育集团未来科技城中学）</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>未来科技城海创园</t>
+          <t>杭州师范大学附属未来科技城中学（杭州二中教育集团未来科技城中学）</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -10754,14 +10770,22 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>未来科技城公办第一</t>
-        </is>
-      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>公办独立初中</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -10774,42 +10798,42 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>杜甫中学</t>
+          <t>杭州维翰学校</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>杭州市余杭区杜甫中学</t>
+          <t>杭州维翰学校</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>良渚街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -10824,34 +10848,34 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>杭州师范大学附属未来科技城中学</t>
+          <t>杭州绿城亲亲学校</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>杭州师范大学附属未来科技城中学</t>
+          <t>杭州绿城亲亲学校</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>杭州二中教育集团核心校，未来科技城核心公办</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -10866,40 +10890,36 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>杭州师范大学附属未来科技城中学（杭州二中教育集团未来科技城中学）</t>
+          <t>杭州绿城育华桃花源学校</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>杭州师范大学附属未来科技城中学（杭州二中教育集团未来科技城中学）</t>
+          <t>杭州绿城育华桃花源学校</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr"/>
+          <t>十二年一贯制</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>含初中部，需摇号</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10912,17 +10932,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>杭州维翰学校</t>
+          <t>杭州绿城育华翡翠城学校</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>杭州维翰学校</t>
+          <t>杭州绿城育华翡翠城学校</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10937,12 +10957,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -10962,17 +10982,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>杭州绿城亲亲学校</t>
+          <t>杭州蕙兰未来科技城学校</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>杭州绿城亲亲学校</t>
+          <t>杭州蕙兰未来科技城学校</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -10982,11 +11002,19 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
+          <t>十二年一贯制</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J235" t="inlineStr">
         <is>
           <t>含初中部，需摇号</t>
@@ -11004,17 +11032,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>杭州绿城育华桃花源学校</t>
+          <t>树兰英才学校（初中部）</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>杭州绿城育华桃花源学校</t>
+          <t>杭州市余杭区树兰英才学校（初中部）</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -11024,16 +11052,20 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>含初中部，需摇号</t>
-        </is>
-      </c>
+          <t>民办初中</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -11046,17 +11078,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>杭州绿城育华翡翠城学校</t>
+          <t>橄榄树学校</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>杭州绿城育华翡翠城学校</t>
+          <t>橄榄树学校</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -11064,24 +11096,12 @@
           <t>民办</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>国际化民办</t>
         </is>
       </c>
     </row>
@@ -11096,42 +11116,42 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>杭州蕙兰未来科技城学校</t>
+          <t>沈括中学</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>杭州蕙兰未来科技城学校</t>
+          <t>杭州市余杭区沈括中学</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>未来科技城公办初中</t>
         </is>
       </c>
     </row>
@@ -11146,40 +11166,44 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>树兰英才学校（初中部）</t>
+          <t>海辰中学</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>杭州市余杭区树兰英才学校（初中部）</t>
+          <t>杭州市余杭区海辰中学</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>民办初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>396</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr"/>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>未来科技城公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -11192,17 +11216,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>橄榄树学校</t>
+          <t>狄邦文理学校（初中部）</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>橄榄树学校</t>
+          <t>杭州市余杭区狄邦文理学校（初中部）</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -11210,14 +11234,22 @@
           <t>民办</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>国际化民办</t>
-        </is>
-      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>民办初中</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -11230,17 +11262,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>沈括中学</t>
+          <t>瓶窑第一中学</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>杭州市余杭区沈括中学</t>
+          <t>杭州市余杭区瓶窑第一中学</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -11255,17 +11287,17 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>670</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>未来科技城公办初中</t>
+          <t>瓶窑镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -11280,17 +11312,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>海辰中学</t>
+          <t>百丈中学</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>杭州市余杭区海辰中学</t>
+          <t>杭州市余杭区百丈中学</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -11303,19 +11335,11 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>未来科技城公办初中</t>
+          <t>百丈镇公办初中</t>
         </is>
       </c>
     </row>
@@ -11330,37 +11354,37 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>狄邦文理学校（初中部）</t>
+          <t>禹航实验学校</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>杭州市余杭区狄邦文理学校（初中部）</t>
+          <t>杭州市余杭区禹航实验学校</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>民办初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>380</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -11376,44 +11400,40 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>瓶窑第一中学</t>
+          <t>绿城育华亲亲</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>杭州市余杭区瓶窑第一中学</t>
+          <t>杭州市余杭区绿城育华亲亲学校（初中部）</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>民办初中</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>瓶窑镇核心公办初中</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -11426,34 +11446,42 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>百丈中学</t>
+          <t>育海外国语</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>杭州市余杭区百丈中学</t>
+          <t>杭州市余杭区育海外国语学校</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>百丈镇公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -11473,12 +11501,12 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>禹航实验学校</t>
+          <t>良渚第一中学</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>杭州市余杭区禹航实验学校</t>
+          <t>杭州市余杭区良渚第一中学</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -11488,20 +11516,24 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>920</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr"/>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>良渚街道核心公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -11514,40 +11546,44 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>绿城育华亲亲</t>
+          <t>良渚第二中学</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>杭州市余杭区绿城育华亲亲学校（初中部）</t>
+          <t>杭州市余杭区良渚第二中学</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>民办初中</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>790</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr"/>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>良渚街道公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -11560,17 +11596,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>育海外国语</t>
+          <t>英特外国语</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>杭州市余杭区育海外国语学校</t>
+          <t>杭州英特外国语学校</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -11585,17 +11621,17 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>410</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>含初中部，需摇号，余杭头部民办</t>
         </is>
       </c>
     </row>
@@ -11610,42 +11646,34 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>良渚第一中学</t>
+          <t>蒲公英学校</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>杭州市余杭区良渚第一中学</t>
+          <t>杭州市余杭区蒲公英学校</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
+          <t>九年一贯制</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
-          <t>良渚街道核心公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -11660,42 +11688,38 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>良渚第二中学</t>
+          <t>蔚澜学校</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>杭州市余杭区良渚第二中学</t>
+          <t>杭州市余杭蔚澜学校</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
-          <t>良渚街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -11710,42 +11734,42 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>英特外国语</t>
+          <t>闲林中学</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>杭州英特外国语学校</t>
+          <t>杭州市余杭区闲林中学</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>含初中部，需摇号，余杭头部民办</t>
+          <t>闲林街道核心公办初中</t>
         </is>
       </c>
     </row>
@@ -11765,29 +11789,29 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>蒲公英学校</t>
+          <t>鸬鸟中学</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>杭州市余杭区蒲公英学校</t>
+          <t>杭州市余杭区鸬鸟中学</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>鸬鸟镇公办初中</t>
         </is>
       </c>
     </row>
@@ -11802,38 +11826,42 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>蔚澜学校</t>
+          <t>黄湖中学</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>杭州市余杭蔚澜学校</t>
+          <t>杭州市余杭区黄湖中学</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr"/>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>黄湖镇公办初中</t>
         </is>
       </c>
     </row>
@@ -11843,22 +11871,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>余杭区</t>
+          <t>临平区</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>闲林中学</t>
+          <t>临平第一中学</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>杭州市余杭区闲林中学</t>
+          <t>杭州市临平区临平第一中学</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -11873,17 +11901,17 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>780</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>123</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>闲林街道核心公办初中</t>
+          <t>含望梅校区、南汇校区，临平核心公办</t>
         </is>
       </c>
     </row>
@@ -11893,22 +11921,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>余杭区</t>
+          <t>临平区</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>鸬鸟中学</t>
+          <t>临平第三中学</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>杭州市余杭区鸬鸟中学</t>
+          <t>杭州市临平区临平第三中学</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -11921,11 +11949,19 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>鸬鸟镇公办初中</t>
+          <t>含梅堰校区、风荷校区，临平城区公办</t>
         </is>
       </c>
     </row>
@@ -11935,22 +11971,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>余杭区</t>
+          <t>临平区</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>黄湖中学</t>
+          <t>临平第二中学</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>杭州市余杭区黄湖中学</t>
+          <t>杭州市临平区临平第二中学</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -11965,17 +12001,17 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>480</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>黄湖镇公办初中</t>
+          <t>临平城区公办初中</t>
         </is>
       </c>
     </row>
@@ -11995,12 +12031,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>临平第一中学</t>
+          <t>临平第五中学</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第一中学</t>
+          <t>杭州市临平区临平第五中学</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -12015,17 +12051,17 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>690</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>131</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>含望梅校区、南汇校区，临平核心公办</t>
+          <t>临平城区公办初中</t>
         </is>
       </c>
     </row>
@@ -12040,17 +12076,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>临平第三中学</t>
+          <t>乔司中学</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第三中学</t>
+          <t>杭州市临平区乔司中学</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -12065,17 +12101,17 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>510</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>含梅堰校区、风荷校区，临平城区公办</t>
+          <t>乔司街道公办初中</t>
         </is>
       </c>
     </row>
@@ -12090,42 +12126,42 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>临平第二中学</t>
+          <t>信达外国语</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第二中学</t>
+          <t>杭州信达外国语学校</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>520</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>临平城区公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -12140,17 +12176,17 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>临平第五中学</t>
+          <t>启文中学</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第五中学</t>
+          <t>杭州市临平区启文中学</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -12165,12 +12201,12 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -12190,17 +12226,17 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>乔司中学</t>
+          <t>启明实验学校</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>杭州市临平区乔司中学</t>
+          <t>杭州市临平区启明实验学校</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -12210,24 +12246,20 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>公办九年一贯制（内设初中部）</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>乔司街道公办初中</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -12240,22 +12272,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>信达外国语</t>
+          <t>吴昌硕实验学校</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>杭州信达外国语学校</t>
+          <t>杭州市临平区吴昌硕实验学校</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -12265,17 +12297,17 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>360</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -12290,17 +12322,17 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>启文中学</t>
+          <t>塘栖第三中学</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>杭州市临平区启文中学</t>
+          <t>杭州市临平区塘栖第三中学</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -12315,17 +12347,17 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>临平城区公办初中</t>
+          <t>2026年新启用公办初中</t>
         </is>
       </c>
     </row>
@@ -12345,12 +12377,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>启明实验学校</t>
+          <t>塘栖第二中学</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>杭州市临平区启明实验学校</t>
+          <t>杭州市临平区塘栖第二中学</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -12360,20 +12392,24 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>公办九年一贯制（内设初中部）</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>400</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr"/>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>塘栖镇核心公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -12386,17 +12422,17 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>吴昌硕实验学校</t>
+          <t>崇贤中学</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>杭州市临平区吴昌硕实验学校</t>
+          <t>杭州市临平区崇贤中学</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -12406,22 +12442,22 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>490</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>崇贤街道公办初中</t>
         </is>
       </c>
     </row>
@@ -12436,17 +12472,17 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>塘栖第三中学</t>
+          <t>星华实验学校</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>杭州市临平区塘栖第三中学</t>
+          <t>杭州市临平区星华实验学校</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -12456,22 +12492,22 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>280</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>2026年新启用公办初中</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -12486,17 +12522,17 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>塘栖第二中学</t>
+          <t>星桥中学</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>杭州市临平区塘栖第二中学</t>
+          <t>杭州市临平区星桥中学</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -12511,17 +12547,17 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>430</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>塘栖镇核心公办初中</t>
+          <t>星桥街道公办初中</t>
         </is>
       </c>
     </row>
@@ -12536,42 +12572,42 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>崇贤中学</t>
+          <t>杭州光华外国语学校</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>杭州市临平区崇贤中学</t>
+          <t>杭州光华外国语学校</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>崇贤街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -12586,22 +12622,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>星华实验学校</t>
+          <t>杭州树兰实验学校</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>杭州市临平区星华实验学校</t>
+          <t>杭州树兰实验学校</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -12611,17 +12647,17 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -12636,42 +12672,42 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>星桥中学</t>
+          <t>杭州橄榄树学校</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>杭州市临平区星桥中学</t>
+          <t>杭州橄榄树学校</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>十二年一贯制</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>星桥街道公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -12686,42 +12722,30 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>杭州光华外国语学校</t>
+          <t>杭高临平学校</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>杭州光华外国语学校</t>
+          <t>杭高临平学校</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>公办</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>杭高教育集团新校</t>
         </is>
       </c>
     </row>
@@ -12736,17 +12760,17 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>杭州树兰实验学校</t>
+          <t>林苑学校</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>杭州树兰实验学校</t>
+          <t>杭州市余杭区林苑学校</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -12759,16 +12783,8 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
           <t>含初中部，需摇号</t>
@@ -12786,42 +12802,42 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>杭州橄榄树学校</t>
+          <t>永进学校</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>杭州橄榄树学校</t>
+          <t>杭州市临平区永进学校</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>十二年一贯制</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>240</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>含初中部</t>
         </is>
       </c>
     </row>
@@ -12841,12 +12857,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>杭高临平学校</t>
+          <t>沾桥中学</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>杭高临平学校</t>
+          <t>杭州市临平区沾桥中学</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -12854,12 +12870,24 @@
           <t>公办</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>杭高教育集团新校</t>
+          <t>崇贤街道公办初中</t>
         </is>
       </c>
     </row>
@@ -12874,36 +12902,40 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>林苑学校</t>
+          <t>第一中学教育集团南汇中学</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>杭州市余杭区林苑学校</t>
+          <t>临平第一中学教育集团南汇中学</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>含初中部，需摇号</t>
-        </is>
-      </c>
+          <t>公办独立初中</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -12916,22 +12948,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>永进学校</t>
+          <t>育蕾学校运河校区</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>杭州市临平区永进学校</t>
+          <t>杭州市余杭区育蕾学校运河校区</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -12939,19 +12971,11 @@
           <t>九年一贯制</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
-          <t>含初中部</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -12966,17 +12990,17 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>沾桥中学</t>
+          <t>运河中学</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>杭州市临平区沾桥中学</t>
+          <t>杭州市临平区运河中学</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -12991,17 +13015,17 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>410</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>崇贤街道公办初中</t>
+          <t>运河街道公办初中</t>
         </is>
       </c>
     </row>
@@ -13011,22 +13035,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>临平区</t>
+          <t>富阳区</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>第一中学教育集团南汇中学</t>
+          <t>万市中学</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>临平第一中学教育集团南汇中学</t>
+          <t>杭州市富阳区万市中学</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -13036,20 +13060,16 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>公办独立初中</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
+          <t>独立初中</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>万市镇公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -13057,7 +13077,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>临平区</t>
+          <t>富阳区</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -13067,29 +13087,29 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>育蕾学校运河校区</t>
+          <t>上官乡中学</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>杭州市余杭区育蕾学校运河校区</t>
+          <t>杭州市富阳区上官乡中学</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>上官乡公办初中</t>
         </is>
       </c>
     </row>
@@ -13099,22 +13119,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>临平区</t>
+          <t>富阳区</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>运河中学</t>
+          <t>东洲中学</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>杭州市临平区运河中学</t>
+          <t>杭州市富阳区东洲中学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -13127,19 +13147,11 @@
           <t>独立初中</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
-          <t>运河街道公办初中</t>
+          <t>东洲街道公办初中</t>
         </is>
       </c>
     </row>
@@ -13154,17 +13166,17 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>万市中学</t>
+          <t>场口镇中学</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>杭州市富阳区万市中学</t>
+          <t>杭州市富阳区场口镇中学</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -13181,7 +13193,7 @@
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
-          <t>万市镇公办初中</t>
+          <t>场口镇公办初中</t>
         </is>
       </c>
     </row>
@@ -13201,12 +13213,12 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>上官乡中学</t>
+          <t>大源中学</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>杭州市富阳区上官乡中学</t>
+          <t>杭州市富阳区大源中学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -13223,7 +13235,7 @@
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
-          <t>上官乡公办初中</t>
+          <t>大源镇公办初中</t>
         </is>
       </c>
     </row>
@@ -13238,17 +13250,17 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>东洲中学</t>
+          <t>富春中学</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>杭州市富阳区东洲中学</t>
+          <t>杭州市富阳区富春中学</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -13265,7 +13277,7 @@
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
-          <t>东洲街道公办初中</t>
+          <t>城区核心公办初中</t>
         </is>
       </c>
     </row>
@@ -13285,12 +13297,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>场口镇中学</t>
+          <t>富春第三中学</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>杭州市富阳区场口镇中学</t>
+          <t>杭州市富阳区富春第三中学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -13307,7 +13319,7 @@
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
-          <t>场口镇公办初中</t>
+          <t>城区核心公办初中</t>
         </is>
       </c>
     </row>
@@ -13327,12 +13339,12 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>大源中学</t>
+          <t>常安镇中学</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>杭州市富阳区大源中学</t>
+          <t>杭州市富阳区常安镇中学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -13349,7 +13361,7 @@
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
-          <t>大源镇公办初中</t>
+          <t>常安镇公办初中</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13376,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>富春中学</t>
+          <t>新登镇中学</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>杭州市富阳区富春中学</t>
+          <t>杭州市富阳区新登镇中学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -13391,7 +13403,7 @@
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
-          <t>城区核心公办初中</t>
+          <t>新登镇核心公办初中</t>
         </is>
       </c>
     </row>
@@ -13406,17 +13418,17 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>富春第三中学</t>
+          <t>春建乡中学</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>杭州市富阳区富春第三中学</t>
+          <t>杭州市富阳区春建乡中学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -13433,7 +13445,7 @@
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
-          <t>城区核心公办初中</t>
+          <t>春建乡公办初中</t>
         </is>
       </c>
     </row>
@@ -13453,12 +13465,12 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>常安镇中学</t>
+          <t>春江中学</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>杭州市富阳区常安镇中学</t>
+          <t>杭州市富阳区春江中学</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -13475,7 +13487,7 @@
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr">
         <is>
-          <t>常安镇公办初中</t>
+          <t>春江街道公办初中</t>
         </is>
       </c>
     </row>
@@ -13490,34 +13502,34 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>新登镇中学</t>
+          <t>杭州上附外国语学校</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>杭州市富阳区新登镇中学</t>
+          <t>杭州上附外国语学校</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
-          <t>新登镇核心公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -13537,29 +13549,29 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>春建乡中学</t>
+          <t>杭州东吴实验学校</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>杭州市富阳区春建乡中学</t>
+          <t>杭州东吴实验学校</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>独立初中</t>
+          <t>九年一贯制</t>
         </is>
       </c>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
-          <t>春建乡公办初中</t>
+          <t>含初中部，需摇号</t>
         </is>
       </c>
     </row>
@@ -13579,17 +13591,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>春江中学</t>
+          <t>杭州银湖实验中学（永兴分校）</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>杭州市富阳区春江中学</t>
+          <t>杭州银湖实验中学（永兴分校）</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -13601,7 +13613,7 @@
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
-          <t>春江街道公办初中</t>
+          <t>需摇号，富阳头部民办</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13628,17 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>杭州上附外国语学校</t>
+          <t>永兴学校</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>杭州上附外国语学校</t>
+          <t>杭州市富阳区永兴学校</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -13663,31 +13675,27 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>杭州东吴实验学校</t>
+          <t>永昌中学</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>杭州东吴实验学校</t>
+          <t>杭州富阳永昌中学</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>含初中部，需摇号</t>
-        </is>
-      </c>
+      <c r="J293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -13705,17 +13713,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>杭州银湖实验中学（永兴分校）</t>
+          <t>湖源乡中学</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>杭州银湖实验中学（永兴分校）</t>
+          <t>杭州市富阳区湖源乡中学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -13727,7 +13735,7 @@
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
-          <t>需摇号，富阳头部民办</t>
+          <t>湖源乡公办初中</t>
         </is>
       </c>
     </row>
@@ -13742,34 +13750,34 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>永兴学校</t>
+          <t>灵桥镇中学</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>杭州市富阳区永兴学校</t>
+          <t>杭州市富阳区灵桥镇中学</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>民办</t>
+          <t>公办</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>九年一贯制</t>
+          <t>独立初中</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
-          <t>含初中部，需摇号</t>
+          <t>灵桥镇公办初中</t>
         </is>
       </c>
     </row>
@@ -13789,12 +13797,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>永昌中学</t>
+          <t>环山中学</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>杭州富阳永昌中学</t>
+          <t>杭州市富阳区环山中学</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -13809,7 +13817,11 @@
       </c>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>环山乡公办初中</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -13827,12 +13839,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>湖源乡中学</t>
+          <t>胥口中学</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>杭州市富阳区湖源乡中学</t>
+          <t>杭州富阳胥口中学</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -13847,11 +13859,7 @@
       </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>湖源乡公办初中</t>
-        </is>
-      </c>
+      <c r="J297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -13869,12 +13877,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>灵桥镇中学</t>
+          <t>贤明中学</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>杭州市富阳区灵桥镇中学</t>
+          <t>杭州市富阳区贤明中学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -13891,7 +13899,7 @@
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr">
         <is>
-          <t>灵桥镇公办初中</t>
+          <t>新登镇公办初中</t>
         </is>
       </c>
     </row>
@@ -13906,17 +13914,17 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>环山中学</t>
+          <t>郁达夫中学</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>杭州市富阳区环山中学</t>
+          <t>杭州市富阳区郁达夫中学</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -13933,7 +13941,7 @@
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
-          <t>环山乡公办初中</t>
+          <t>含达夫校区、文豪校区，城区核心公办</t>
         </is>
       </c>
     </row>
@@ -13953,12 +13961,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>胥口中学</t>
+          <t>里山镇中学</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>杭州富阳胥口中学</t>
+          <t>杭州富阳里山镇中学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -13991,12 +13999,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>贤明中学</t>
+          <t>银湖中学</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>杭州市富阳区贤明中学</t>
+          <t>杭州市富阳区银湖中学</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -14013,7 +14021,7 @@
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
-          <t>新登镇公办初中</t>
+          <t>银湖街道核心公办初中</t>
         </is>
       </c>
     </row>
@@ -14028,17 +14036,17 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>郁达夫中学</t>
+          <t>银湖中学（受降中学）</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>杭州市富阳区郁达夫中学</t>
+          <t>杭州市富阳区银湖中学（受降中学）</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -14055,7 +14063,7 @@
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
-          <t>含达夫校区、文豪校区，城区核心公办</t>
+          <t>银湖街道核心公办初中</t>
         </is>
       </c>
     </row>
@@ -14070,22 +14078,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>里山镇中学</t>
+          <t>银湖实验</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>杭州富阳里山镇中学</t>
+          <t>杭州银湖实验中学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>公办</t>
+          <t>民办</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -14095,7 +14103,11 @@
       </c>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr"/>
-      <c r="J303" t="inlineStr"/>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>需摇号，富阳头部民办</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -14113,12 +14125,12 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>银湖中学</t>
+          <t>高桥中学</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>杭州市富阳区银湖中学</t>
+          <t>杭州富阳区高桥中学</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -14133,11 +14145,7 @@
       </c>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>银湖街道核心公办初中</t>
-        </is>
-      </c>
+      <c r="J304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -14155,12 +14163,12 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>银湖中学（受降中学）</t>
+          <t>鹿山中学</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>杭州市富阳区银湖中学（受降中学）</t>
+          <t>杭州市富阳区鹿山中学</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -14176,128 +14184,6 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
-        <is>
-          <t>银湖街道核心公办初中</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>305</v>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>富阳区</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>银湖实验</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>杭州银湖实验中学</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>民办</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr"/>
-      <c r="I306" t="inlineStr"/>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>需摇号，富阳头部民办</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>306</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>富阳区</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>高桥中学</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>杭州富阳区高桥中学</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr"/>
-      <c r="I307" t="inlineStr"/>
-      <c r="J307" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>307</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>富阳区</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>鹿山中学</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>杭州市富阳区鹿山中学</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>公办</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>独立初中</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr">
         <is>
           <t>鹿山街道公办初中</t>
         </is>
